--- a/deparacontabil1.xlsx
+++ b/deparacontabil1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\123.0.0.62\power bi\2.DashBoards\Resultado Sintetico Operacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0261CDA-8DC3-42B9-9483-367B7EC55B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FCF306-8C0E-4FB6-AAEA-784A26A8A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="526">
   <si>
     <t>Item_DRE</t>
   </si>
@@ -1609,6 +1609,15 @@
   </si>
   <si>
     <t>AÇÚCAR CRISTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3.2.3.01.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3.2.3.03.013</t>
+  </si>
+  <si>
+    <t>FUNERAIS</t>
   </si>
 </sst>
 </file>
@@ -2281,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="13">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="D1" s="13">
         <v>46022</v>
@@ -2320,7 +2329,7 @@
       </c>
       <c r="C2" s="16">
         <f>-SUMIF(Planilha1!H:H,Export!A2,Planilha1!G:G)/1000</f>
-        <v>66782.783420000007</v>
+        <v>67367.32729999999</v>
       </c>
       <c r="D2" s="16">
         <v>183977.59916000001</v>
@@ -2359,7 +2368,7 @@
       </c>
       <c r="C3" s="16">
         <f>C2</f>
-        <v>66782.783420000007</v>
+        <v>67367.32729999999</v>
       </c>
       <c r="D3" s="16">
         <v>183977.59916000001</v>
@@ -2398,7 +2407,7 @@
       </c>
       <c r="C4" s="16">
         <f>-SUMIF(Planilha1!H:H,Export!A4,Planilha1!G:G)/1000</f>
-        <v>-236.92765999999921</v>
+        <v>-210.42917999999969</v>
       </c>
       <c r="D4" s="16">
         <v>-10820.206029999999</v>
@@ -2473,7 +2482,7 @@
       </c>
       <c r="C6" s="16">
         <f>C2+C4</f>
-        <v>66545.855760000006</v>
+        <v>67156.898119999983</v>
       </c>
       <c r="D6" s="16">
         <v>173157.39313000001</v>
@@ -2620,7 +2629,7 @@
       </c>
       <c r="C10" s="16">
         <f>C6+C7+C9</f>
-        <v>-13429.461749999988</v>
+        <v>-12818.41939000001</v>
       </c>
       <c r="D10" s="16">
         <v>-24223.817520000011</v>
@@ -2662,7 +2671,7 @@
       </c>
       <c r="C11" s="16">
         <f>SUM(C12:C16)</f>
-        <v>-10486.524009999997</v>
+        <v>-14316.17188</v>
       </c>
       <c r="D11" s="16">
         <v>-21196.787099999994</v>
@@ -2704,7 +2713,7 @@
       </c>
       <c r="C12" s="16">
         <f>-SUMIF(Planilha1!H:H,Export!A12,Planilha1!G:G)/1000</f>
-        <v>-2896.0713500000002</v>
+        <v>-2992.7024000000001</v>
       </c>
       <c r="D12" s="16">
         <v>-10072.414939999997</v>
@@ -2743,7 +2752,7 @@
       </c>
       <c r="C13" s="16">
         <f>-SUMIF(Planilha1!H:H,Export!A13,Planilha1!G:G)/1000</f>
-        <v>-7856.7716299999975</v>
+        <v>-11529.088009999999</v>
       </c>
       <c r="D13" s="16">
         <v>-23424.206990000002</v>
@@ -2782,7 +2791,7 @@
       </c>
       <c r="C14" s="16">
         <f>-SUMIF(Planilha1!H:H,Export!A14,Planilha1!G:G)/1000</f>
-        <v>435.34792999999996</v>
+        <v>374.64749</v>
       </c>
       <c r="D14" s="16">
         <v>600.92124000000001</v>
@@ -2905,7 +2914,7 @@
       </c>
       <c r="C17" s="16">
         <f>C10+C11</f>
-        <v>-23915.985759999985</v>
+        <v>-27134.591270000012</v>
       </c>
       <c r="D17" s="16">
         <v>-45420.604620000006</v>
@@ -2947,7 +2956,7 @@
       </c>
       <c r="C18" s="16">
         <f>-SUMIF(Planilha1!H:H,Export!A18,Planilha1!G:G)/1000</f>
-        <v>-3898.9235700000004</v>
+        <v>-7294.794609999999</v>
       </c>
       <c r="D18" s="16">
         <v>-13173.99727</v>
@@ -3022,7 +3031,7 @@
       </c>
       <c r="C20" s="16">
         <f>C17+C18</f>
-        <v>-27814.909329999984</v>
+        <v>-34429.385880000009</v>
       </c>
       <c r="D20" s="16">
         <v>-58594.601890000005</v>
@@ -3140,7 +3149,7 @@
       </c>
       <c r="C23" s="23">
         <f>C20</f>
-        <v>-27814.909329999984</v>
+        <v>-34429.385880000009</v>
       </c>
       <c r="D23" s="23">
         <v>-58594.601890000005</v>
@@ -3181,7 +3190,7 @@
       </c>
       <c r="C24" s="16">
         <f t="shared" ref="C24" si="0">C23-C16</f>
-        <v>-27645.880369999984</v>
+        <v>-34260.356920000006</v>
       </c>
       <c r="D24" s="16">
         <v>-65443.537160000007</v>
@@ -3234,7 +3243,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1955832-B42A-4228-A9E5-3BCF3F9D5B31}">
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -3330,19 +3339,19 @@
         <v>66</v>
       </c>
       <c r="C8" s="57">
-        <v>25301530.640000001</v>
+        <v>30812786.699999999</v>
       </c>
       <c r="D8" s="57">
-        <v>20898594.43</v>
+        <v>11922670.689999999</v>
       </c>
       <c r="E8" s="57">
-        <v>18385215.739999998</v>
+        <v>8306071.5099999998</v>
       </c>
       <c r="F8" s="57">
-        <v>2513378.69</v>
+        <v>3616599.18</v>
       </c>
       <c r="G8" s="57">
-        <v>27814909.329999998</v>
+        <v>34429385.880000003</v>
       </c>
       <c r="H8" t="str">
         <f>_xlfn.XLOOKUP(A8,indice!A:A,indice!C:C)</f>
@@ -3357,19 +3366,19 @@
         <v>68</v>
       </c>
       <c r="C9" s="57">
-        <v>-58132400.060000002</v>
+        <v>-67289635.909999996</v>
       </c>
       <c r="D9" s="57">
-        <v>60797.279999999999</v>
+        <v>0</v>
       </c>
       <c r="E9" s="57">
-        <v>8711180.6400000006</v>
+        <v>77691.39</v>
       </c>
       <c r="F9" s="57">
-        <v>-8650383.3599999994</v>
+        <v>-77691.39</v>
       </c>
       <c r="G9" s="57">
-        <v>-66782783.420000002</v>
+        <v>-67367327.299999997</v>
       </c>
       <c r="H9" t="str">
         <f>_xlfn.XLOOKUP(A9,indice!A:A,indice!C:C)</f>
@@ -3384,19 +3393,19 @@
         <v>70</v>
       </c>
       <c r="C10" s="57">
-        <v>-58132400.060000002</v>
+        <v>-67289635.909999996</v>
       </c>
       <c r="D10" s="57">
-        <v>60797.279999999999</v>
+        <v>0</v>
       </c>
       <c r="E10" s="57">
-        <v>8711180.6400000006</v>
+        <v>77691.39</v>
       </c>
       <c r="F10" s="57">
-        <v>-8650383.3599999994</v>
+        <v>-77691.39</v>
       </c>
       <c r="G10" s="57">
-        <v>-66782783.420000002</v>
+        <v>-67367327.299999997</v>
       </c>
       <c r="H10" t="str">
         <f>_xlfn.XLOOKUP(A10,indice!A:A,indice!C:C)</f>
@@ -3546,19 +3555,19 @@
         <v>77</v>
       </c>
       <c r="C16" s="57">
-        <v>-32400989.02</v>
+        <v>-40846334.920000002</v>
       </c>
       <c r="D16" s="57">
         <v>0</v>
       </c>
       <c r="E16" s="57">
-        <v>7961824.4100000001</v>
+        <v>77691.39</v>
       </c>
       <c r="F16" s="57">
-        <v>-7961824.4100000001</v>
+        <v>-77691.39</v>
       </c>
       <c r="G16" s="57">
-        <v>-40362813.43</v>
+        <v>-40924026.310000002</v>
       </c>
       <c r="H16" t="str">
         <f>_xlfn.XLOOKUP(A16,indice!A:A,indice!C:C)</f>
@@ -3573,19 +3582,19 @@
         <v>59</v>
       </c>
       <c r="C17" s="57">
-        <v>-32400989.02</v>
+        <v>-40846334.920000002</v>
       </c>
       <c r="D17" s="57">
         <v>0</v>
       </c>
       <c r="E17" s="57">
-        <v>7961824.4100000001</v>
+        <v>77691.39</v>
       </c>
       <c r="F17" s="57">
-        <v>-7961824.4100000001</v>
+        <v>-77691.39</v>
       </c>
       <c r="G17" s="57">
-        <v>-40362813.43</v>
+        <v>-40924026.310000002</v>
       </c>
       <c r="H17">
         <f>_xlfn.XLOOKUP(A17,indice!A:A,indice!C:C)</f>
@@ -3600,16 +3609,16 @@
         <v>80</v>
       </c>
       <c r="C18" s="57">
-        <v>-4290</v>
+        <v>-5460</v>
       </c>
       <c r="D18" s="57">
         <v>0</v>
       </c>
       <c r="E18" s="57">
-        <v>1170</v>
+        <v>0</v>
       </c>
       <c r="F18" s="57">
-        <v>-1170</v>
+        <v>0</v>
       </c>
       <c r="G18" s="57">
         <v>-5460</v>
@@ -3627,16 +3636,16 @@
         <v>84</v>
       </c>
       <c r="C19" s="57">
-        <v>-4290</v>
+        <v>-5460</v>
       </c>
       <c r="D19" s="57">
         <v>0</v>
       </c>
       <c r="E19" s="57">
-        <v>1170</v>
+        <v>0</v>
       </c>
       <c r="F19" s="57">
-        <v>-1170</v>
+        <v>0</v>
       </c>
       <c r="G19" s="57">
         <v>-5460</v>
@@ -3654,19 +3663,19 @@
         <v>90</v>
       </c>
       <c r="C20" s="57">
-        <v>-62230</v>
+        <v>-92848</v>
       </c>
       <c r="D20" s="57">
         <v>0</v>
       </c>
       <c r="E20" s="57">
-        <v>7287</v>
+        <v>0</v>
       </c>
       <c r="F20" s="57">
-        <v>-7287</v>
+        <v>0</v>
       </c>
       <c r="G20" s="57">
-        <v>-69517</v>
+        <v>-92848</v>
       </c>
       <c r="H20" t="str">
         <f>_xlfn.XLOOKUP(A20,indice!A:A,indice!C:C)</f>
@@ -3681,19 +3690,19 @@
         <v>92</v>
       </c>
       <c r="C21" s="57">
-        <v>-62230</v>
+        <v>-92848</v>
       </c>
       <c r="D21" s="57">
         <v>0</v>
       </c>
       <c r="E21" s="57">
-        <v>7287</v>
+        <v>0</v>
       </c>
       <c r="F21" s="57">
-        <v>-7287</v>
+        <v>0</v>
       </c>
       <c r="G21" s="57">
-        <v>-69517</v>
+        <v>-92848</v>
       </c>
       <c r="H21">
         <f>_xlfn.XLOOKUP(A21,indice!A:A,indice!C:C)</f>
@@ -3708,16 +3717,16 @@
         <v>434</v>
       </c>
       <c r="C22" s="57">
-        <v>-123930.22</v>
+        <v>-804032.17</v>
       </c>
       <c r="D22" s="57">
-        <v>60797.279999999999</v>
+        <v>0</v>
       </c>
       <c r="E22" s="57">
-        <v>740899.23</v>
+        <v>0</v>
       </c>
       <c r="F22" s="57">
-        <v>-680101.95</v>
+        <v>0</v>
       </c>
       <c r="G22" s="57">
         <v>-804032.17</v>
@@ -3735,16 +3744,16 @@
         <v>436</v>
       </c>
       <c r="C23" s="57">
-        <v>-123930.22</v>
+        <v>-804032.17</v>
       </c>
       <c r="D23" s="57">
-        <v>60797.279999999999</v>
+        <v>0</v>
       </c>
       <c r="E23" s="57">
-        <v>740899.23</v>
+        <v>0</v>
       </c>
       <c r="F23" s="57">
-        <v>-680101.95</v>
+        <v>0</v>
       </c>
       <c r="G23" s="57">
         <v>-804032.17</v>
@@ -3762,19 +3771,19 @@
         <v>94</v>
       </c>
       <c r="C24" s="57">
-        <v>83433930.700000003</v>
+        <v>98102422.609999999</v>
       </c>
       <c r="D24" s="57">
-        <v>20837797.149999999</v>
+        <v>11922670.689999999</v>
       </c>
       <c r="E24" s="57">
-        <v>9674035.0999999996</v>
+        <v>8228380.1200000001</v>
       </c>
       <c r="F24" s="57">
-        <v>11163762.050000001</v>
+        <v>3694290.57</v>
       </c>
       <c r="G24" s="57">
-        <v>94597692.75</v>
+        <v>101796713.18000001</v>
       </c>
       <c r="H24" t="str">
         <f>_xlfn.XLOOKUP(A24,indice!A:A,indice!C:C)</f>
@@ -3789,19 +3798,19 @@
         <v>96</v>
       </c>
       <c r="C25" s="57">
-        <v>4442517.96</v>
+        <v>4460111.18</v>
       </c>
       <c r="D25" s="57">
-        <v>10418.93</v>
+        <v>0</v>
       </c>
       <c r="E25" s="57">
         <v>0</v>
       </c>
       <c r="F25" s="57">
-        <v>10418.93</v>
+        <v>0</v>
       </c>
       <c r="G25" s="57">
-        <v>4452936.8899999997</v>
+        <v>4460111.18</v>
       </c>
       <c r="H25" t="str">
         <f>_xlfn.XLOOKUP(A25,indice!A:A,indice!C:C)</f>
@@ -3816,16 +3825,16 @@
         <v>98</v>
       </c>
       <c r="C26" s="57">
-        <v>4415123.59</v>
+        <v>4422859.5</v>
       </c>
       <c r="D26" s="57">
-        <v>7735.91</v>
+        <v>0</v>
       </c>
       <c r="E26" s="57">
         <v>0</v>
       </c>
       <c r="F26" s="57">
-        <v>7735.91</v>
+        <v>0</v>
       </c>
       <c r="G26" s="57">
         <v>4422859.5</v>
@@ -3897,16 +3906,16 @@
         <v>102</v>
       </c>
       <c r="C29" s="57">
-        <v>255513.75</v>
+        <v>256893.67</v>
       </c>
       <c r="D29" s="57">
-        <v>1379.92</v>
+        <v>0</v>
       </c>
       <c r="E29" s="57">
         <v>0</v>
       </c>
       <c r="F29" s="57">
-        <v>1379.92</v>
+        <v>0</v>
       </c>
       <c r="G29" s="57">
         <v>256893.67</v>
@@ -3924,16 +3933,16 @@
         <v>104</v>
       </c>
       <c r="C30" s="57">
-        <v>1175029.98</v>
+        <v>1181385.97</v>
       </c>
       <c r="D30" s="57">
-        <v>6355.99</v>
+        <v>0</v>
       </c>
       <c r="E30" s="57">
         <v>0</v>
       </c>
       <c r="F30" s="57">
-        <v>6355.99</v>
+        <v>0</v>
       </c>
       <c r="G30" s="57">
         <v>1181385.97</v>
@@ -4005,19 +4014,19 @@
         <v>110</v>
       </c>
       <c r="C33" s="57">
-        <v>27394.37</v>
+        <v>37251.68</v>
       </c>
       <c r="D33" s="57">
-        <v>2683.02</v>
+        <v>0</v>
       </c>
       <c r="E33" s="57">
         <v>0</v>
       </c>
       <c r="F33" s="57">
-        <v>2683.02</v>
+        <v>0</v>
       </c>
       <c r="G33" s="57">
-        <v>30077.39</v>
+        <v>37251.68</v>
       </c>
       <c r="H33" t="str">
         <f>_xlfn.XLOOKUP(A33,indice!A:A,indice!C:C)</f>
@@ -4032,19 +4041,19 @@
         <v>56</v>
       </c>
       <c r="C34" s="57">
-        <v>21241.26</v>
+        <v>28158.17</v>
       </c>
       <c r="D34" s="57">
-        <v>1900.74</v>
+        <v>0</v>
       </c>
       <c r="E34" s="57">
         <v>0</v>
       </c>
       <c r="F34" s="57">
-        <v>1900.74</v>
+        <v>0</v>
       </c>
       <c r="G34" s="57">
-        <v>23142</v>
+        <v>28158.17</v>
       </c>
       <c r="H34">
         <f>_xlfn.XLOOKUP(A34,indice!A:A,indice!C:C)</f>
@@ -4059,19 +4068,19 @@
         <v>113</v>
       </c>
       <c r="C35" s="57">
-        <v>1097.5899999999999</v>
+        <v>1622.1</v>
       </c>
       <c r="D35" s="57">
-        <v>139.55000000000001</v>
+        <v>0</v>
       </c>
       <c r="E35" s="57">
         <v>0</v>
       </c>
       <c r="F35" s="57">
-        <v>139.55000000000001</v>
+        <v>0</v>
       </c>
       <c r="G35" s="57">
-        <v>1237.1400000000001</v>
+        <v>1622.1</v>
       </c>
       <c r="H35">
         <f>_xlfn.XLOOKUP(A35,indice!A:A,indice!C:C)</f>
@@ -4086,19 +4095,19 @@
         <v>115</v>
       </c>
       <c r="C36" s="57">
-        <v>5055.5200000000004</v>
+        <v>7471.41</v>
       </c>
       <c r="D36" s="57">
-        <v>642.73</v>
+        <v>0</v>
       </c>
       <c r="E36" s="57">
         <v>0</v>
       </c>
       <c r="F36" s="57">
-        <v>642.73</v>
+        <v>0</v>
       </c>
       <c r="G36" s="57">
-        <v>5698.25</v>
+        <v>7471.41</v>
       </c>
       <c r="H36">
         <f>_xlfn.XLOOKUP(A36,indice!A:A,indice!C:C)</f>
@@ -4113,16 +4122,16 @@
         <v>12</v>
       </c>
       <c r="C37" s="57">
-        <v>70577240.689999998</v>
+        <v>79975317.510000005</v>
       </c>
       <c r="D37" s="57">
-        <v>9398076.8200000003</v>
+        <v>0</v>
       </c>
       <c r="E37" s="57">
         <v>0</v>
       </c>
       <c r="F37" s="57">
-        <v>9398076.8200000003</v>
+        <v>0</v>
       </c>
       <c r="G37" s="57">
         <v>79975317.510000005</v>
@@ -4140,16 +4149,16 @@
         <v>118</v>
       </c>
       <c r="C38" s="57">
-        <v>70577240.689999998</v>
+        <v>79063852.129999995</v>
       </c>
       <c r="D38" s="57">
-        <v>8486611.4399999995</v>
+        <v>0</v>
       </c>
       <c r="E38" s="57">
         <v>0</v>
       </c>
       <c r="F38" s="57">
-        <v>8486611.4399999995</v>
+        <v>0</v>
       </c>
       <c r="G38" s="57">
         <v>79063852.129999995</v>
@@ -4248,16 +4257,16 @@
         <v>59</v>
       </c>
       <c r="C42" s="57">
-        <v>45284918.549999997</v>
+        <v>53771529.990000002</v>
       </c>
       <c r="D42" s="57">
-        <v>8486611.4399999995</v>
+        <v>0</v>
       </c>
       <c r="E42" s="57">
         <v>0</v>
       </c>
       <c r="F42" s="57">
-        <v>8486611.4399999995</v>
+        <v>0</v>
       </c>
       <c r="G42" s="57">
         <v>53771529.990000002</v>
@@ -4275,16 +4284,16 @@
         <v>125</v>
       </c>
       <c r="C43" s="57">
-        <v>0</v>
+        <v>911465.38</v>
       </c>
       <c r="D43" s="57">
-        <v>911465.38</v>
+        <v>0</v>
       </c>
       <c r="E43" s="57">
         <v>0</v>
       </c>
       <c r="F43" s="57">
-        <v>911465.38</v>
+        <v>0</v>
       </c>
       <c r="G43" s="57">
         <v>911465.38</v>
@@ -4302,16 +4311,16 @@
         <v>127</v>
       </c>
       <c r="C44" s="57">
-        <v>0</v>
+        <v>911465.38</v>
       </c>
       <c r="D44" s="57">
-        <v>911465.38</v>
+        <v>0</v>
       </c>
       <c r="E44" s="57">
         <v>0</v>
       </c>
       <c r="F44" s="57">
-        <v>911465.38</v>
+        <v>0</v>
       </c>
       <c r="G44" s="57">
         <v>911465.38</v>
@@ -4329,19 +4338,19 @@
         <v>129</v>
       </c>
       <c r="C45" s="57">
-        <v>8414172.0500000007</v>
+        <v>13666993.92</v>
       </c>
       <c r="D45" s="57">
-        <v>11429301.4</v>
+        <v>11922670.689999999</v>
       </c>
       <c r="E45" s="57">
-        <v>9674035.0999999996</v>
+        <v>8228380.1200000001</v>
       </c>
       <c r="F45" s="57">
-        <v>1755266.3</v>
+        <v>3694290.57</v>
       </c>
       <c r="G45" s="57">
-        <v>10169438.35</v>
+        <v>17361284.489999998</v>
       </c>
       <c r="H45" t="str">
         <f>_xlfn.XLOOKUP(A45,indice!A:A,indice!C:C)</f>
@@ -4359,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="D46" s="57">
-        <v>8153346.0999999996</v>
+        <v>8170613.6100000003</v>
       </c>
       <c r="E46" s="57">
-        <v>8153346.0999999996</v>
+        <v>8170613.6100000003</v>
       </c>
       <c r="F46" s="57">
         <v>0</v>
@@ -4383,19 +4392,19 @@
         <v>133</v>
       </c>
       <c r="C47" s="57">
-        <v>11276974.83</v>
+        <v>14346960.779999999</v>
       </c>
       <c r="D47" s="57">
-        <v>1432262.83</v>
+        <v>1601990.43</v>
       </c>
       <c r="E47" s="57">
-        <v>2131.62</v>
+        <v>2027.87</v>
       </c>
       <c r="F47" s="57">
-        <v>1430131.21</v>
+        <v>1599962.56</v>
       </c>
       <c r="G47" s="57">
-        <v>12707106.039999999</v>
+        <v>15946923.34</v>
       </c>
       <c r="H47" t="str">
         <f>_xlfn.XLOOKUP(A47,indice!A:A,indice!C:C)</f>
@@ -4410,19 +4419,19 @@
         <v>135</v>
       </c>
       <c r="C48" s="57">
-        <v>1145605</v>
+        <v>1589089.18</v>
       </c>
       <c r="D48" s="57">
-        <v>215095.75</v>
+        <v>233815.55</v>
       </c>
       <c r="E48" s="57">
-        <v>513.84</v>
+        <v>61.72</v>
       </c>
       <c r="F48" s="57">
-        <v>214581.91</v>
+        <v>233753.83</v>
       </c>
       <c r="G48" s="57">
-        <v>1360186.91</v>
+        <v>1822843.01</v>
       </c>
       <c r="H48" t="str">
         <f>_xlfn.XLOOKUP(A48,indice!A:A,indice!C:C)</f>
@@ -4437,19 +4446,19 @@
         <v>137</v>
       </c>
       <c r="C49" s="57">
-        <v>1410749.33</v>
+        <v>1946115.6</v>
       </c>
       <c r="D49" s="57">
-        <v>288215.32</v>
+        <v>306177.26</v>
       </c>
       <c r="E49" s="57">
-        <v>24181.24</v>
+        <v>8954.4699999999993</v>
       </c>
       <c r="F49" s="57">
-        <v>264034.08</v>
+        <v>297222.78999999998</v>
       </c>
       <c r="G49" s="57">
-        <v>1674783.41</v>
+        <v>2243338.39</v>
       </c>
       <c r="H49" t="str">
         <f>_xlfn.XLOOKUP(A49,indice!A:A,indice!C:C)</f>
@@ -4464,19 +4473,19 @@
         <v>63</v>
       </c>
       <c r="C50" s="57">
-        <v>35648.199999999997</v>
+        <v>66443.81</v>
       </c>
       <c r="D50" s="57">
-        <v>22013.73</v>
+        <v>23373.200000000001</v>
       </c>
       <c r="E50" s="57">
-        <v>12985.88</v>
+        <v>437.64</v>
       </c>
       <c r="F50" s="57">
-        <v>9027.85</v>
+        <v>22935.56</v>
       </c>
       <c r="G50" s="57">
-        <v>44676.05</v>
+        <v>89379.37</v>
       </c>
       <c r="H50" t="str">
         <f>_xlfn.XLOOKUP(A50,indice!A:A,indice!C:C)</f>
@@ -4491,19 +4500,19 @@
         <v>64</v>
       </c>
       <c r="C51" s="57">
-        <v>1160587.8899999999</v>
+        <v>1490336.42</v>
       </c>
       <c r="D51" s="57">
-        <v>182842.38</v>
+        <v>191320.27</v>
       </c>
       <c r="E51" s="57">
-        <v>35374.04</v>
+        <v>744.88</v>
       </c>
       <c r="F51" s="57">
-        <v>147468.34</v>
+        <v>190575.39</v>
       </c>
       <c r="G51" s="57">
-        <v>1308056.23</v>
+        <v>1680911.81</v>
       </c>
       <c r="H51" t="str">
         <f>_xlfn.XLOOKUP(A51,indice!A:A,indice!C:C)</f>
@@ -4539,25 +4548,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>523</v>
       </c>
       <c r="B53" t="s">
-        <v>143</v>
+        <v>277</v>
       </c>
       <c r="C53" s="57">
-        <v>45628.59</v>
+        <v>0</v>
       </c>
       <c r="D53" s="57">
-        <v>475.96</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="E53" s="57">
         <v>0</v>
       </c>
       <c r="F53" s="57">
-        <v>475.96</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="G53" s="57">
-        <v>46104.55</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="H53" t="str">
         <f>_xlfn.XLOOKUP(A53,indice!A:A,indice!C:C)</f>
@@ -4566,25 +4575,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C54" s="57">
-        <v>4929.2</v>
+        <v>46452.15</v>
       </c>
       <c r="D54" s="57">
-        <v>973.7</v>
+        <v>1863.35</v>
       </c>
       <c r="E54" s="57">
         <v>0</v>
       </c>
       <c r="F54" s="57">
-        <v>973.7</v>
+        <v>1863.35</v>
       </c>
       <c r="G54" s="57">
-        <v>5902.9</v>
+        <v>48315.5</v>
       </c>
       <c r="H54" t="str">
         <f>_xlfn.XLOOKUP(A54,indice!A:A,indice!C:C)</f>
@@ -4593,25 +4602,25 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C55" s="57">
-        <v>14261.99</v>
+        <v>7296</v>
       </c>
       <c r="D55" s="57">
-        <v>2500</v>
+        <v>669.1</v>
       </c>
       <c r="E55" s="57">
         <v>0</v>
       </c>
       <c r="F55" s="57">
-        <v>2500</v>
+        <v>669.1</v>
       </c>
       <c r="G55" s="57">
-        <v>16761.990000000002</v>
+        <v>7965.1</v>
       </c>
       <c r="H55" t="str">
         <f>_xlfn.XLOOKUP(A55,indice!A:A,indice!C:C)</f>
@@ -4620,25 +4629,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C56" s="57">
-        <v>8089.9</v>
+        <v>21729.56</v>
       </c>
       <c r="D56" s="57">
-        <v>4044.95</v>
+        <v>12633.26</v>
       </c>
       <c r="E56" s="57">
         <v>0</v>
       </c>
       <c r="F56" s="57">
-        <v>4044.95</v>
+        <v>12633.26</v>
       </c>
       <c r="G56" s="57">
-        <v>12134.85</v>
+        <v>34362.82</v>
       </c>
       <c r="H56" t="str">
         <f>_xlfn.XLOOKUP(A56,indice!A:A,indice!C:C)</f>
@@ -4647,25 +4656,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C57" s="57">
-        <v>2722766.87</v>
+        <v>0</v>
       </c>
       <c r="D57" s="57">
-        <v>386336.52</v>
+        <v>26</v>
       </c>
       <c r="E57" s="57">
-        <v>32814.51</v>
+        <v>0</v>
       </c>
       <c r="F57" s="57">
-        <v>353522.01</v>
+        <v>26</v>
       </c>
       <c r="G57" s="57">
-        <v>3076288.88</v>
+        <v>26</v>
       </c>
       <c r="H57" t="str">
         <f>_xlfn.XLOOKUP(A57,indice!A:A,indice!C:C)</f>
@@ -4674,25 +4683,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C58" s="57">
-        <v>641217.38</v>
+        <v>20224.75</v>
       </c>
       <c r="D58" s="57">
-        <v>0</v>
+        <v>4044.95</v>
       </c>
       <c r="E58" s="57">
         <v>0</v>
       </c>
       <c r="F58" s="57">
-        <v>0</v>
+        <v>4044.95</v>
       </c>
       <c r="G58" s="57">
-        <v>641217.38</v>
+        <v>24269.7</v>
       </c>
       <c r="H58" t="str">
         <f>_xlfn.XLOOKUP(A58,indice!A:A,indice!C:C)</f>
@@ -4701,25 +4710,25 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B59" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C59" s="57">
-        <v>800250.02</v>
+        <v>3347511.29</v>
       </c>
       <c r="D59" s="57">
-        <v>417494.43</v>
+        <v>742230.1</v>
       </c>
       <c r="E59" s="57">
-        <v>0</v>
+        <v>63592.82</v>
       </c>
       <c r="F59" s="57">
-        <v>417494.43</v>
+        <v>678637.28</v>
       </c>
       <c r="G59" s="57">
-        <v>1217744.45</v>
+        <v>4026148.57</v>
       </c>
       <c r="H59" t="str">
         <f>_xlfn.XLOOKUP(A59,indice!A:A,indice!C:C)</f>
@@ -4728,25 +4737,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B60" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C60" s="57">
-        <v>941357.3</v>
+        <v>641217.38</v>
       </c>
       <c r="D60" s="57">
-        <v>116529.43</v>
+        <v>0</v>
       </c>
       <c r="E60" s="57">
-        <v>8529.3799999999992</v>
+        <v>0</v>
       </c>
       <c r="F60" s="57">
-        <v>108000.05</v>
+        <v>0</v>
       </c>
       <c r="G60" s="57">
-        <v>1049357.3500000001</v>
+        <v>641217.38</v>
       </c>
       <c r="H60" t="str">
         <f>_xlfn.XLOOKUP(A60,indice!A:A,indice!C:C)</f>
@@ -4755,25 +4764,25 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C61" s="57">
-        <v>3510494.77</v>
+        <v>1232404.3899999999</v>
       </c>
       <c r="D61" s="57">
-        <v>2106722.46</v>
+        <v>0</v>
       </c>
       <c r="E61" s="57">
-        <v>186387.08</v>
+        <v>0</v>
       </c>
       <c r="F61" s="57">
-        <v>1920335.38</v>
+        <v>0</v>
       </c>
       <c r="G61" s="57">
-        <v>5430830.1500000004</v>
+        <v>1232404.3899999999</v>
       </c>
       <c r="H61" t="str">
         <f>_xlfn.XLOOKUP(A61,indice!A:A,indice!C:C)</f>
@@ -4782,25 +4791,25 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C62" s="57">
-        <v>63839.73</v>
+        <v>1234536.73</v>
       </c>
       <c r="D62" s="57">
-        <v>21279.91</v>
+        <v>189623.19</v>
       </c>
       <c r="E62" s="57">
-        <v>0</v>
+        <v>14546.94</v>
       </c>
       <c r="F62" s="57">
-        <v>21279.91</v>
+        <v>175076.25</v>
       </c>
       <c r="G62" s="57">
-        <v>85119.64</v>
+        <v>1409612.98</v>
       </c>
       <c r="H62" t="str">
         <f>_xlfn.XLOOKUP(A62,indice!A:A,indice!C:C)</f>
@@ -4809,25 +4818,25 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B63" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C63" s="57">
-        <v>41377.760000000002</v>
+        <v>5891074.4800000004</v>
       </c>
       <c r="D63" s="57">
-        <v>14970.02</v>
+        <v>474646.37</v>
       </c>
       <c r="E63" s="57">
-        <v>0</v>
+        <v>34599.83</v>
       </c>
       <c r="F63" s="57">
-        <v>14970.02</v>
+        <v>440046.54</v>
       </c>
       <c r="G63" s="57">
-        <v>56347.78</v>
+        <v>6331121.0199999996</v>
       </c>
       <c r="H63" t="str">
         <f>_xlfn.XLOOKUP(A63,indice!A:A,indice!C:C)</f>
@@ -4836,25 +4845,25 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C64" s="57">
-        <v>7206.22</v>
+        <v>106399.55</v>
       </c>
       <c r="D64" s="57">
-        <v>11082.49</v>
+        <v>21279.91</v>
       </c>
       <c r="E64" s="57">
         <v>0</v>
       </c>
       <c r="F64" s="57">
-        <v>11082.49</v>
+        <v>21279.91</v>
       </c>
       <c r="G64" s="57">
-        <v>18288.71</v>
+        <v>127679.46</v>
       </c>
       <c r="H64" t="str">
         <f>_xlfn.XLOOKUP(A64,indice!A:A,indice!C:C)</f>
@@ -4863,25 +4872,25 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C65" s="57">
-        <v>38831.14</v>
+        <v>92673.08</v>
       </c>
       <c r="D65" s="57">
-        <v>4065.4</v>
+        <v>14139.45</v>
       </c>
       <c r="E65" s="57">
-        <v>10.29</v>
+        <v>0</v>
       </c>
       <c r="F65" s="57">
-        <v>4055.11</v>
+        <v>14139.45</v>
       </c>
       <c r="G65" s="57">
-        <v>42886.25</v>
+        <v>106812.53</v>
       </c>
       <c r="H65" t="str">
         <f>_xlfn.XLOOKUP(A65,indice!A:A,indice!C:C)</f>
@@ -4890,25 +4899,25 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B66" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C66" s="57">
-        <v>4596117.46</v>
+        <v>18513.400000000001</v>
       </c>
       <c r="D66" s="57">
-        <v>314711.43</v>
+        <v>100.21</v>
       </c>
       <c r="E66" s="57">
         <v>0</v>
       </c>
       <c r="F66" s="57">
-        <v>314711.43</v>
+        <v>100.21</v>
       </c>
       <c r="G66" s="57">
-        <v>4910828.8899999997</v>
+        <v>18613.61</v>
       </c>
       <c r="H66" t="str">
         <f>_xlfn.XLOOKUP(A66,indice!A:A,indice!C:C)</f>
@@ -4917,13 +4926,13 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B67" t="s">
-        <v>238</v>
+        <v>394</v>
       </c>
       <c r="C67" s="57">
-        <v>176.69</v>
+        <v>14998.8</v>
       </c>
       <c r="D67" s="57">
         <v>0</v>
@@ -4935,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="57">
-        <v>176.69</v>
+        <v>14998.8</v>
       </c>
       <c r="H67" t="str">
         <f>_xlfn.XLOOKUP(A67,indice!A:A,indice!C:C)</f>
@@ -4944,25 +4953,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B68" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C68" s="57">
-        <v>119.4</v>
+        <v>48976.3</v>
       </c>
       <c r="D68" s="57">
-        <v>0</v>
+        <v>26632.71</v>
       </c>
       <c r="E68" s="57">
         <v>0</v>
       </c>
       <c r="F68" s="57">
-        <v>0</v>
+        <v>26632.71</v>
       </c>
       <c r="G68" s="57">
-        <v>119.4</v>
+        <v>75609.009999999995</v>
       </c>
       <c r="H68" t="str">
         <f>_xlfn.XLOOKUP(A68,indice!A:A,indice!C:C)</f>
@@ -4971,25 +4980,25 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B69" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C69" s="57">
-        <v>806422.57</v>
+        <v>5183565.8099999996</v>
       </c>
       <c r="D69" s="57">
-        <v>0</v>
+        <v>344785.38</v>
       </c>
       <c r="E69" s="57">
         <v>0</v>
       </c>
       <c r="F69" s="57">
-        <v>0</v>
+        <v>344785.38</v>
       </c>
       <c r="G69" s="57">
-        <v>806422.57</v>
+        <v>5528351.1900000004</v>
       </c>
       <c r="H69" t="str">
         <f>_xlfn.XLOOKUP(A69,indice!A:A,indice!C:C)</f>
@@ -4998,25 +5007,25 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>180</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="C70" s="57">
-        <v>5295455.8600000003</v>
+        <v>176.69</v>
       </c>
       <c r="D70" s="57">
-        <v>640469.61</v>
+        <v>97.9</v>
       </c>
       <c r="E70" s="57">
         <v>0</v>
       </c>
       <c r="F70" s="57">
-        <v>640469.61</v>
+        <v>97.9</v>
       </c>
       <c r="G70" s="57">
-        <v>5935925.4699999997</v>
+        <v>274.58999999999997</v>
       </c>
       <c r="H70" t="str">
         <f>_xlfn.XLOOKUP(A70,indice!A:A,indice!C:C)</f>
@@ -5025,25 +5034,25 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B71" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C71" s="57">
-        <v>1968722.4</v>
+        <v>165.4</v>
       </c>
       <c r="D71" s="57">
-        <v>178132.5</v>
+        <v>0</v>
       </c>
       <c r="E71" s="57">
         <v>0</v>
       </c>
       <c r="F71" s="57">
-        <v>178132.5</v>
+        <v>0</v>
       </c>
       <c r="G71" s="57">
-        <v>2146854.9</v>
+        <v>165.4</v>
       </c>
       <c r="H71" t="str">
         <f>_xlfn.XLOOKUP(A71,indice!A:A,indice!C:C)</f>
@@ -5052,25 +5061,25 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>427</v>
+        <v>178</v>
       </c>
       <c r="B72" t="s">
-        <v>428</v>
+        <v>179</v>
       </c>
       <c r="C72" s="57">
-        <v>67776.44</v>
+        <v>806422.57</v>
       </c>
       <c r="D72" s="57">
-        <v>62637.52</v>
+        <v>235.93</v>
       </c>
       <c r="E72" s="57">
         <v>0</v>
       </c>
       <c r="F72" s="57">
-        <v>62637.52</v>
+        <v>235.93</v>
       </c>
       <c r="G72" s="57">
-        <v>130413.96</v>
+        <v>806658.5</v>
       </c>
       <c r="H72" t="str">
         <f>_xlfn.XLOOKUP(A72,indice!A:A,indice!C:C)</f>
@@ -5079,25 +5088,25 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B73" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C73" s="57">
-        <v>13063783.68</v>
+        <v>6847866.3200000003</v>
       </c>
       <c r="D73" s="57">
-        <v>0</v>
+        <v>413704.91</v>
       </c>
       <c r="E73" s="57">
         <v>0</v>
       </c>
       <c r="F73" s="57">
-        <v>0</v>
+        <v>413704.91</v>
       </c>
       <c r="G73" s="57">
-        <v>13063783.68</v>
+        <v>7261571.2300000004</v>
       </c>
       <c r="H73" t="str">
         <f>_xlfn.XLOOKUP(A73,indice!A:A,indice!C:C)</f>
@@ -5106,25 +5115,25 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B74" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C74" s="57">
-        <v>1663060.67</v>
+        <v>3052491.38</v>
       </c>
       <c r="D74" s="57">
-        <v>173710.07999999999</v>
+        <v>866188.65</v>
       </c>
       <c r="E74" s="57">
-        <v>1136.32</v>
+        <v>0</v>
       </c>
       <c r="F74" s="57">
-        <v>172573.76</v>
+        <v>866188.65</v>
       </c>
       <c r="G74" s="57">
-        <v>1835634.43</v>
+        <v>3918680.03</v>
       </c>
       <c r="H74" t="str">
         <f>_xlfn.XLOOKUP(A74,indice!A:A,indice!C:C)</f>
@@ -5133,25 +5142,25 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>188</v>
+        <v>427</v>
       </c>
       <c r="B75" t="s">
-        <v>189</v>
+        <v>428</v>
       </c>
       <c r="C75" s="57">
-        <v>12656.27</v>
+        <v>130413.96</v>
       </c>
       <c r="D75" s="57">
-        <v>3627.75</v>
+        <v>0</v>
       </c>
       <c r="E75" s="57">
         <v>0</v>
       </c>
       <c r="F75" s="57">
-        <v>3627.75</v>
+        <v>0</v>
       </c>
       <c r="G75" s="57">
-        <v>16284.02</v>
+        <v>130413.96</v>
       </c>
       <c r="H75" t="str">
         <f>_xlfn.XLOOKUP(A75,indice!A:A,indice!C:C)</f>
@@ -5160,25 +5169,25 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C76" s="57">
-        <v>3689357.93</v>
+        <v>13063783.68</v>
       </c>
       <c r="D76" s="57">
-        <v>1261158.97</v>
+        <v>0</v>
       </c>
       <c r="E76" s="57">
-        <v>33119.629999999997</v>
+        <v>0</v>
       </c>
       <c r="F76" s="57">
-        <v>1228039.3400000001</v>
+        <v>0</v>
       </c>
       <c r="G76" s="57">
-        <v>4917397.2699999996</v>
+        <v>13063783.68</v>
       </c>
       <c r="H76" t="str">
         <f>_xlfn.XLOOKUP(A76,indice!A:A,indice!C:C)</f>
@@ -5187,25 +5196,25 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C77" s="57">
-        <v>4013851.2</v>
+        <v>2428216.56</v>
       </c>
       <c r="D77" s="57">
-        <v>0</v>
+        <v>1115590.06</v>
       </c>
       <c r="E77" s="57">
-        <v>0</v>
+        <v>183.41</v>
       </c>
       <c r="F77" s="57">
-        <v>0</v>
+        <v>1115406.6499999999</v>
       </c>
       <c r="G77" s="57">
-        <v>4013851.2</v>
+        <v>3543623.21</v>
       </c>
       <c r="H77" t="str">
         <f>_xlfn.XLOOKUP(A77,indice!A:A,indice!C:C)</f>
@@ -5214,25 +5223,25 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>443</v>
+        <v>188</v>
       </c>
       <c r="B78" t="s">
-        <v>444</v>
+        <v>189</v>
       </c>
       <c r="C78" s="57">
-        <v>28708</v>
+        <v>23142.85</v>
       </c>
       <c r="D78" s="57">
-        <v>0</v>
+        <v>4050.18</v>
       </c>
       <c r="E78" s="57">
         <v>0</v>
       </c>
       <c r="F78" s="57">
-        <v>0</v>
+        <v>4050.18</v>
       </c>
       <c r="G78" s="57">
-        <v>28708</v>
+        <v>27193.03</v>
       </c>
       <c r="H78" t="str">
         <f>_xlfn.XLOOKUP(A78,indice!A:A,indice!C:C)</f>
@@ -5241,25 +5250,25 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C79" s="57">
-        <v>81576.98</v>
+        <v>5916450.6299999999</v>
       </c>
       <c r="D79" s="57">
-        <v>22755.24</v>
+        <v>1256948.7</v>
       </c>
       <c r="E79" s="57">
-        <v>119.8</v>
+        <v>256546.85</v>
       </c>
       <c r="F79" s="57">
-        <v>22635.439999999999</v>
+        <v>1000401.85</v>
       </c>
       <c r="G79" s="57">
-        <v>104212.42</v>
+        <v>6916852.4800000004</v>
       </c>
       <c r="H79" t="str">
         <f>_xlfn.XLOOKUP(A79,indice!A:A,indice!C:C)</f>
@@ -5268,25 +5277,25 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>516</v>
+        <v>192</v>
       </c>
       <c r="B80" t="s">
-        <v>315</v>
+        <v>193</v>
       </c>
       <c r="C80" s="57">
-        <v>0</v>
+        <v>4013851.2</v>
       </c>
       <c r="D80" s="57">
-        <v>1345.26</v>
+        <v>0</v>
       </c>
       <c r="E80" s="57">
         <v>0</v>
       </c>
       <c r="F80" s="57">
-        <v>1345.26</v>
+        <v>0</v>
       </c>
       <c r="G80" s="57">
-        <v>1345.26</v>
+        <v>4013851.2</v>
       </c>
       <c r="H80" t="str">
         <f>_xlfn.XLOOKUP(A80,indice!A:A,indice!C:C)</f>
@@ -5295,25 +5304,25 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>196</v>
+        <v>443</v>
       </c>
       <c r="B81" t="s">
-        <v>197</v>
+        <v>444</v>
       </c>
       <c r="C81" s="57">
-        <v>25392562.469999999</v>
+        <v>28708</v>
       </c>
       <c r="D81" s="57">
         <v>0</v>
       </c>
       <c r="E81" s="57">
-        <v>0</v>
+        <v>1364.59</v>
       </c>
       <c r="F81" s="57">
-        <v>0</v>
+        <v>-1364.59</v>
       </c>
       <c r="G81" s="57">
-        <v>25392562.469999999</v>
+        <v>27343.41</v>
       </c>
       <c r="H81" t="str">
         <f>_xlfn.XLOOKUP(A81,indice!A:A,indice!C:C)</f>
@@ -5322,25 +5331,25 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B82" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C82" s="57">
-        <v>-107667.75</v>
+        <v>125651.81</v>
       </c>
       <c r="D82" s="57">
-        <v>0</v>
+        <v>35554.120000000003</v>
       </c>
       <c r="E82" s="57">
-        <v>12296</v>
+        <v>0</v>
       </c>
       <c r="F82" s="57">
-        <v>-12296</v>
+        <v>35554.120000000003</v>
       </c>
       <c r="G82" s="57">
-        <v>-119963.75</v>
+        <v>161205.93</v>
       </c>
       <c r="H82" t="str">
         <f>_xlfn.XLOOKUP(A82,indice!A:A,indice!C:C)</f>
@@ -5349,25 +5358,25 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>200</v>
+        <v>516</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>315</v>
       </c>
       <c r="C83" s="57">
-        <v>886316.49</v>
+        <v>3744.68</v>
       </c>
       <c r="D83" s="57">
-        <v>37429.71</v>
+        <v>0</v>
       </c>
       <c r="E83" s="57">
         <v>0</v>
       </c>
       <c r="F83" s="57">
-        <v>37429.71</v>
+        <v>0</v>
       </c>
       <c r="G83" s="57">
-        <v>923746.2</v>
+        <v>3744.68</v>
       </c>
       <c r="H83" t="str">
         <f>_xlfn.XLOOKUP(A83,indice!A:A,indice!C:C)</f>
@@ -5376,25 +5385,25 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C84" s="57">
-        <v>82760.66</v>
+        <v>25392562.469999999</v>
       </c>
       <c r="D84" s="57">
-        <v>18461.8</v>
+        <v>0</v>
       </c>
       <c r="E84" s="57">
         <v>0</v>
       </c>
       <c r="F84" s="57">
-        <v>18461.8</v>
+        <v>0</v>
       </c>
       <c r="G84" s="57">
-        <v>101222.46</v>
+        <v>25392562.469999999</v>
       </c>
       <c r="H84" t="str">
         <f>_xlfn.XLOOKUP(A84,indice!A:A,indice!C:C)</f>
@@ -5403,25 +5412,25 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B85" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C85" s="57">
-        <v>360510.4</v>
+        <v>-135114.67000000001</v>
       </c>
       <c r="D85" s="57">
-        <v>87858.2</v>
+        <v>1364.59</v>
       </c>
       <c r="E85" s="57">
-        <v>0</v>
+        <v>7823.69</v>
       </c>
       <c r="F85" s="57">
-        <v>87858.2</v>
+        <v>-6459.1</v>
       </c>
       <c r="G85" s="57">
-        <v>448368.6</v>
+        <v>-141573.76999999999</v>
       </c>
       <c r="H85" t="str">
         <f>_xlfn.XLOOKUP(A85,indice!A:A,indice!C:C)</f>
@@ -5430,25 +5439,25 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B86" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C86" s="57">
-        <v>230534.64</v>
+        <v>962665.73</v>
       </c>
       <c r="D86" s="57">
-        <v>32857.769999999997</v>
+        <v>46090.65</v>
       </c>
       <c r="E86" s="57">
         <v>0</v>
       </c>
       <c r="F86" s="57">
-        <v>32857.769999999997</v>
+        <v>46090.65</v>
       </c>
       <c r="G86" s="57">
-        <v>263392.40999999997</v>
+        <v>1008756.38</v>
       </c>
       <c r="H86" t="str">
         <f>_xlfn.XLOOKUP(A86,indice!A:A,indice!C:C)</f>
@@ -5457,25 +5466,25 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B87" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C87" s="57">
-        <v>278332.73</v>
+        <v>118806.7</v>
       </c>
       <c r="D87" s="57">
-        <v>13079.52</v>
+        <v>18992.849999999999</v>
       </c>
       <c r="E87" s="57">
         <v>0</v>
       </c>
       <c r="F87" s="57">
-        <v>13079.52</v>
+        <v>18992.849999999999</v>
       </c>
       <c r="G87" s="57">
-        <v>291412.25</v>
+        <v>137799.54999999999</v>
       </c>
       <c r="H87" t="str">
         <f>_xlfn.XLOOKUP(A87,indice!A:A,indice!C:C)</f>
@@ -5484,25 +5493,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B88" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C88" s="57">
-        <v>216010.22</v>
+        <v>540841.25</v>
       </c>
       <c r="D88" s="57">
-        <v>7824.6</v>
+        <v>97233.63</v>
       </c>
       <c r="E88" s="57">
         <v>0</v>
       </c>
       <c r="F88" s="57">
-        <v>7824.6</v>
+        <v>97233.63</v>
       </c>
       <c r="G88" s="57">
-        <v>223834.82</v>
+        <v>638074.88</v>
       </c>
       <c r="H88" t="str">
         <f>_xlfn.XLOOKUP(A88,indice!A:A,indice!C:C)</f>
@@ -5511,25 +5520,25 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B89" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C89" s="57">
-        <v>159399.75</v>
+        <v>287890.73</v>
       </c>
       <c r="D89" s="57">
-        <v>1850</v>
+        <v>27872.65</v>
       </c>
       <c r="E89" s="57">
         <v>0</v>
       </c>
       <c r="F89" s="57">
-        <v>1850</v>
+        <v>27872.65</v>
       </c>
       <c r="G89" s="57">
-        <v>161249.75</v>
+        <v>315763.38</v>
       </c>
       <c r="H89" t="str">
         <f>_xlfn.XLOOKUP(A89,indice!A:A,indice!C:C)</f>
@@ -5538,25 +5547,25 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B90" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C90" s="57">
-        <v>-87197255.620000005</v>
+        <v>291725.27</v>
       </c>
       <c r="D90" s="57">
         <v>0</v>
       </c>
       <c r="E90" s="57">
-        <v>7803746.4699999997</v>
+        <v>0</v>
       </c>
       <c r="F90" s="57">
-        <v>-7803746.4699999997</v>
+        <v>0</v>
       </c>
       <c r="G90" s="57">
-        <v>-95001002.090000004</v>
+        <v>291725.27</v>
       </c>
       <c r="H90" t="str">
         <f>_xlfn.XLOOKUP(A90,indice!A:A,indice!C:C)</f>
@@ -5565,25 +5574,25 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B91" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C91" s="57">
-        <v>539696.68000000005</v>
+        <v>232916.42</v>
       </c>
       <c r="D91" s="57">
-        <v>68530.86</v>
+        <v>9974.5300000000007</v>
       </c>
       <c r="E91" s="57">
         <v>0</v>
       </c>
       <c r="F91" s="57">
-        <v>68530.86</v>
+        <v>9974.5300000000007</v>
       </c>
       <c r="G91" s="57">
-        <v>608227.54</v>
+        <v>242890.95</v>
       </c>
       <c r="H91" t="str">
         <f>_xlfn.XLOOKUP(A91,indice!A:A,indice!C:C)</f>
@@ -5592,121 +5601,121 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B92" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C92" s="57">
-        <v>2855480.04</v>
+        <v>168683.42</v>
       </c>
       <c r="D92" s="57">
-        <v>43096.639999999999</v>
+        <v>9643.31</v>
       </c>
       <c r="E92" s="57">
-        <v>2505.33</v>
+        <v>0</v>
       </c>
       <c r="F92" s="57">
-        <v>40591.31</v>
+        <v>9643.31</v>
       </c>
       <c r="G92" s="57">
-        <v>2896071.35</v>
+        <v>178326.73</v>
       </c>
       <c r="H92" t="str">
         <f>_xlfn.XLOOKUP(A92,indice!A:A,indice!C:C)</f>
-        <v>S</v>
+        <v>C</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B93" t="s">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="C93" s="57">
-        <v>46837.11</v>
+        <v>-102331775.94</v>
       </c>
       <c r="D93" s="57">
         <v>0</v>
       </c>
       <c r="E93" s="57">
-        <v>0</v>
+        <v>7779728.9000000004</v>
       </c>
       <c r="F93" s="57">
-        <v>0</v>
+        <v>-7779728.9000000004</v>
       </c>
       <c r="G93" s="57">
-        <v>46837.11</v>
-      </c>
-      <c r="H93">
+        <v>-110111504.84</v>
+      </c>
+      <c r="H93" t="str">
         <f>_xlfn.XLOOKUP(A93,indice!A:A,indice!C:C)</f>
-        <v>10</v>
+        <v>C</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B94" t="s">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="C94" s="57">
-        <v>4122.03</v>
+        <v>681995.77</v>
       </c>
       <c r="D94" s="57">
-        <v>0</v>
+        <v>77700.41</v>
       </c>
       <c r="E94" s="57">
         <v>0</v>
       </c>
       <c r="F94" s="57">
-        <v>0</v>
+        <v>77700.41</v>
       </c>
       <c r="G94" s="57">
-        <v>4122.03</v>
-      </c>
-      <c r="H94">
+        <v>759696.18</v>
+      </c>
+      <c r="H94" t="str">
         <f>_xlfn.XLOOKUP(A94,indice!A:A,indice!C:C)</f>
-        <v>10</v>
+        <v>C</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B95" t="s">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="C95" s="57">
-        <v>5332.71</v>
+        <v>2961620.94</v>
       </c>
       <c r="D95" s="57">
-        <v>0</v>
+        <v>35392.660000000003</v>
       </c>
       <c r="E95" s="57">
-        <v>0</v>
+        <v>4311.2</v>
       </c>
       <c r="F95" s="57">
-        <v>0</v>
+        <v>31081.46</v>
       </c>
       <c r="G95" s="57">
-        <v>5332.71</v>
-      </c>
-      <c r="H95">
+        <v>2992702.4</v>
+      </c>
+      <c r="H95" t="str">
         <f>_xlfn.XLOOKUP(A95,indice!A:A,indice!C:C)</f>
-        <v>10</v>
+        <v>S</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B96" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="C96" s="57">
-        <v>-26.1</v>
+        <v>46837.11</v>
       </c>
       <c r="D96" s="57">
         <v>0</v>
@@ -5718,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="57">
-        <v>-26.1</v>
+        <v>46837.11</v>
       </c>
       <c r="H96">
         <f>_xlfn.XLOOKUP(A96,indice!A:A,indice!C:C)</f>
@@ -5727,13 +5736,13 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B97" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="C97" s="57">
-        <v>4479.16</v>
+        <v>4122.03</v>
       </c>
       <c r="D97" s="57">
         <v>0</v>
@@ -5745,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="57">
-        <v>4479.16</v>
+        <v>4122.03</v>
       </c>
       <c r="H97">
         <f>_xlfn.XLOOKUP(A97,indice!A:A,indice!C:C)</f>
@@ -5754,13 +5763,13 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B98" t="s">
-        <v>228</v>
+        <v>137</v>
       </c>
       <c r="C98" s="57">
-        <v>34.979999999999997</v>
+        <v>5332.71</v>
       </c>
       <c r="D98" s="57">
         <v>0</v>
@@ -5772,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="57">
-        <v>34.979999999999997</v>
+        <v>5332.71</v>
       </c>
       <c r="H98">
         <f>_xlfn.XLOOKUP(A98,indice!A:A,indice!C:C)</f>
@@ -5781,13 +5790,13 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>396</v>
+        <v>225</v>
       </c>
       <c r="B99" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="C99" s="57">
-        <v>-65</v>
+        <v>-26.1</v>
       </c>
       <c r="D99" s="57">
         <v>0</v>
@@ -5799,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="57">
-        <v>-65</v>
+        <v>-26.1</v>
       </c>
       <c r="H99">
         <f>_xlfn.XLOOKUP(A99,indice!A:A,indice!C:C)</f>
@@ -5808,13 +5817,13 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B100" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="C100" s="57">
-        <v>53</v>
+        <v>4479.16</v>
       </c>
       <c r="D100" s="57">
         <v>0</v>
@@ -5826,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="57">
-        <v>53</v>
+        <v>4479.16</v>
       </c>
       <c r="H100">
         <f>_xlfn.XLOOKUP(A100,indice!A:A,indice!C:C)</f>
@@ -5835,25 +5844,25 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B101" t="s">
-        <v>155</v>
+        <v>228</v>
       </c>
       <c r="C101" s="57">
-        <v>110743.57</v>
+        <v>34.979999999999997</v>
       </c>
       <c r="D101" s="57">
-        <v>34769.83</v>
+        <v>0</v>
       </c>
       <c r="E101" s="57">
-        <v>2505.33</v>
+        <v>0</v>
       </c>
       <c r="F101" s="57">
-        <v>32264.5</v>
+        <v>0</v>
       </c>
       <c r="G101" s="57">
-        <v>143008.07</v>
+        <v>34.979999999999997</v>
       </c>
       <c r="H101">
         <f>_xlfn.XLOOKUP(A101,indice!A:A,indice!C:C)</f>
@@ -5862,13 +5871,13 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>231</v>
+        <v>396</v>
       </c>
       <c r="B102" t="s">
-        <v>232</v>
+        <v>145</v>
       </c>
       <c r="C102" s="57">
-        <v>445758.97</v>
+        <v>-65</v>
       </c>
       <c r="D102" s="57">
         <v>0</v>
@@ -5880,7 +5889,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="57">
-        <v>445758.97</v>
+        <v>-65</v>
       </c>
       <c r="H102">
         <f>_xlfn.XLOOKUP(A102,indice!A:A,indice!C:C)</f>
@@ -5889,13 +5898,13 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B103" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C103" s="57">
-        <v>248.37</v>
+        <v>53</v>
       </c>
       <c r="D103" s="57">
         <v>0</v>
@@ -5907,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="57">
-        <v>248.37</v>
+        <v>53</v>
       </c>
       <c r="H103">
         <f>_xlfn.XLOOKUP(A103,indice!A:A,indice!C:C)</f>
@@ -5916,25 +5925,25 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>473</v>
+        <v>230</v>
       </c>
       <c r="B104" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C104" s="57">
-        <v>46794.79</v>
+        <v>169456.89</v>
       </c>
       <c r="D104" s="57">
-        <v>0</v>
+        <v>28751.43</v>
       </c>
       <c r="E104" s="57">
-        <v>0</v>
+        <v>2503.34</v>
       </c>
       <c r="F104" s="57">
-        <v>0</v>
+        <v>26248.09</v>
       </c>
       <c r="G104" s="57">
-        <v>46794.79</v>
+        <v>195704.98</v>
       </c>
       <c r="H104">
         <f>_xlfn.XLOOKUP(A104,indice!A:A,indice!C:C)</f>
@@ -5943,13 +5952,13 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>414</v>
+        <v>231</v>
       </c>
       <c r="B105" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="C105" s="57">
-        <v>826.8</v>
+        <v>445758.97</v>
       </c>
       <c r="D105" s="57">
         <v>0</v>
@@ -5961,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="57">
-        <v>826.8</v>
+        <v>445758.97</v>
       </c>
       <c r="H105">
         <f>_xlfn.XLOOKUP(A105,indice!A:A,indice!C:C)</f>
@@ -5970,13 +5979,13 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B106" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C106" s="57">
-        <v>561.05999999999995</v>
+        <v>248.37</v>
       </c>
       <c r="D106" s="57">
         <v>0</v>
@@ -5988,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="57">
-        <v>561.05999999999995</v>
+        <v>248.37</v>
       </c>
       <c r="H106">
         <f>_xlfn.XLOOKUP(A106,indice!A:A,indice!C:C)</f>
@@ -5997,25 +6006,25 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>235</v>
+        <v>473</v>
       </c>
       <c r="B107" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
       <c r="C107" s="57">
-        <v>171406.86</v>
+        <v>46794.79</v>
       </c>
       <c r="D107" s="57">
-        <v>1851.12</v>
+        <v>0</v>
       </c>
       <c r="E107" s="57">
         <v>0</v>
       </c>
       <c r="F107" s="57">
-        <v>1851.12</v>
+        <v>0</v>
       </c>
       <c r="G107" s="57">
-        <v>173257.98</v>
+        <v>46794.79</v>
       </c>
       <c r="H107">
         <f>_xlfn.XLOOKUP(A107,indice!A:A,indice!C:C)</f>
@@ -6024,25 +6033,25 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>237</v>
+        <v>414</v>
       </c>
       <c r="B108" t="s">
-        <v>238</v>
+        <v>171</v>
       </c>
       <c r="C108" s="57">
-        <v>1050</v>
+        <v>826.8</v>
       </c>
       <c r="D108" s="57">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="E108" s="57">
         <v>0</v>
       </c>
       <c r="F108" s="57">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G108" s="57">
-        <v>1050</v>
+        <v>909.8</v>
       </c>
       <c r="H108">
         <f>_xlfn.XLOOKUP(A108,indice!A:A,indice!C:C)</f>
@@ -6051,25 +6060,25 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>445</v>
+        <v>234</v>
       </c>
       <c r="B109" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C109" s="57">
-        <v>55520.85</v>
+        <v>561.05999999999995</v>
       </c>
       <c r="D109" s="57">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E109" s="57">
         <v>0</v>
       </c>
       <c r="F109" s="57">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G109" s="57">
-        <v>55520.85</v>
+        <v>623.05999999999995</v>
       </c>
       <c r="H109">
         <f>_xlfn.XLOOKUP(A109,indice!A:A,indice!C:C)</f>
@@ -6078,13 +6087,13 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B110" t="s">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="C110" s="57">
-        <v>4282.03</v>
+        <v>173272.38</v>
       </c>
       <c r="D110" s="57">
         <v>0</v>
@@ -6096,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="57">
-        <v>4282.03</v>
+        <v>173272.38</v>
       </c>
       <c r="H110">
         <f>_xlfn.XLOOKUP(A110,indice!A:A,indice!C:C)</f>
@@ -6105,13 +6114,13 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B111" t="s">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="C111" s="57">
-        <v>11938.25</v>
+        <v>1050</v>
       </c>
       <c r="D111" s="57">
         <v>0</v>
@@ -6123,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="57">
-        <v>11938.25</v>
+        <v>1050</v>
       </c>
       <c r="H111">
         <f>_xlfn.XLOOKUP(A111,indice!A:A,indice!C:C)</f>
@@ -6132,13 +6141,13 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="B112" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C112" s="57">
-        <v>209.4</v>
+        <v>55520.85</v>
       </c>
       <c r="D112" s="57">
         <v>0</v>
@@ -6150,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="57">
-        <v>209.4</v>
+        <v>55520.85</v>
       </c>
       <c r="H112">
         <f>_xlfn.XLOOKUP(A112,indice!A:A,indice!C:C)</f>
@@ -6159,25 +6168,25 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B113" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C113" s="57">
-        <v>19427.07</v>
+        <v>4282.03</v>
       </c>
       <c r="D113" s="57">
-        <v>6475.69</v>
+        <v>0</v>
       </c>
       <c r="E113" s="57">
         <v>0</v>
       </c>
       <c r="F113" s="57">
-        <v>6475.69</v>
+        <v>0</v>
       </c>
       <c r="G113" s="57">
-        <v>25902.76</v>
+        <v>4282.03</v>
       </c>
       <c r="H113">
         <f>_xlfn.XLOOKUP(A113,indice!A:A,indice!C:C)</f>
@@ -6186,25 +6195,25 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B114" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="C114" s="57">
-        <v>12.69</v>
+        <v>13078.18</v>
       </c>
       <c r="D114" s="57">
-        <v>0</v>
+        <v>18.66</v>
       </c>
       <c r="E114" s="57">
         <v>0</v>
       </c>
       <c r="F114" s="57">
-        <v>0</v>
+        <v>18.66</v>
       </c>
       <c r="G114" s="57">
-        <v>12.69</v>
+        <v>13096.84</v>
       </c>
       <c r="H114">
         <f>_xlfn.XLOOKUP(A114,indice!A:A,indice!C:C)</f>
@@ -6213,13 +6222,13 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B115" t="s">
-        <v>461</v>
+        <v>189</v>
       </c>
       <c r="C115" s="57">
-        <v>-52.74</v>
+        <v>209.4</v>
       </c>
       <c r="D115" s="57">
         <v>0</v>
@@ -6231,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="57">
-        <v>-52.74</v>
+        <v>209.4</v>
       </c>
       <c r="H115">
         <f>_xlfn.XLOOKUP(A115,indice!A:A,indice!C:C)</f>
@@ -6240,25 +6249,25 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C116" s="57">
-        <v>1662.23</v>
+        <v>23349.200000000001</v>
       </c>
       <c r="D116" s="57">
-        <v>0</v>
+        <v>6477.57</v>
       </c>
       <c r="E116" s="57">
-        <v>0</v>
+        <v>1807.86</v>
       </c>
       <c r="F116" s="57">
-        <v>0</v>
+        <v>4669.71</v>
       </c>
       <c r="G116" s="57">
-        <v>1662.23</v>
+        <v>28018.91</v>
       </c>
       <c r="H116">
         <f>_xlfn.XLOOKUP(A116,indice!A:A,indice!C:C)</f>
@@ -6267,13 +6276,13 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B117" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C117" s="57">
-        <v>1365.64</v>
+        <v>12.69</v>
       </c>
       <c r="D117" s="57">
         <v>0</v>
@@ -6285,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="57">
-        <v>1365.64</v>
+        <v>12.69</v>
       </c>
       <c r="H117">
         <f>_xlfn.XLOOKUP(A117,indice!A:A,indice!C:C)</f>
@@ -6294,13 +6303,13 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>249</v>
+        <v>460</v>
       </c>
       <c r="B118" t="s">
-        <v>211</v>
+        <v>461</v>
       </c>
       <c r="C118" s="57">
-        <v>1137.1400000000001</v>
+        <v>-52.74</v>
       </c>
       <c r="D118" s="57">
         <v>0</v>
@@ -6312,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="57">
-        <v>1137.1400000000001</v>
+        <v>-52.74</v>
       </c>
       <c r="H118">
         <f>_xlfn.XLOOKUP(A118,indice!A:A,indice!C:C)</f>
@@ -6321,13 +6330,13 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B119" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C119" s="57">
-        <v>1565.27</v>
+        <v>1662.23</v>
       </c>
       <c r="D119" s="57">
         <v>0</v>
@@ -6339,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="57">
-        <v>1565.27</v>
+        <v>1662.23</v>
       </c>
       <c r="H119">
         <f>_xlfn.XLOOKUP(A119,indice!A:A,indice!C:C)</f>
@@ -6348,13 +6357,13 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B120" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C120" s="57">
-        <v>510041.52</v>
+        <v>1365.64</v>
       </c>
       <c r="D120" s="57">
         <v>0</v>
@@ -6366,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="57">
-        <v>510041.52</v>
+        <v>1365.64</v>
       </c>
       <c r="H120">
         <f>_xlfn.XLOOKUP(A120,indice!A:A,indice!C:C)</f>
@@ -6375,13 +6384,13 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B121" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C121" s="57">
-        <v>1938.38</v>
+        <v>1137.1400000000001</v>
       </c>
       <c r="D121" s="57">
         <v>0</v>
@@ -6393,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="57">
-        <v>1938.38</v>
+        <v>1137.1400000000001</v>
       </c>
       <c r="H121">
         <f>_xlfn.XLOOKUP(A121,indice!A:A,indice!C:C)</f>
@@ -6402,13 +6411,13 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B122" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="C122" s="57">
-        <v>165635.67000000001</v>
+        <v>1565.27</v>
       </c>
       <c r="D122" s="57">
         <v>0</v>
@@ -6420,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="57">
-        <v>165635.67000000001</v>
+        <v>1565.27</v>
       </c>
       <c r="H122">
         <f>_xlfn.XLOOKUP(A122,indice!A:A,indice!C:C)</f>
@@ -6429,13 +6438,13 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B123" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C123" s="57">
-        <v>1230560.1499999999</v>
+        <v>510041.52</v>
       </c>
       <c r="D123" s="57">
         <v>0</v>
@@ -6447,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="57">
-        <v>1230560.1499999999</v>
+        <v>510041.52</v>
       </c>
       <c r="H123">
         <f>_xlfn.XLOOKUP(A123,indice!A:A,indice!C:C)</f>
@@ -6456,13 +6465,13 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>446</v>
+        <v>253</v>
       </c>
       <c r="B124" t="s">
-        <v>447</v>
+        <v>217</v>
       </c>
       <c r="C124" s="57">
-        <v>12078.18</v>
+        <v>1938.38</v>
       </c>
       <c r="D124" s="57">
         <v>0</v>
@@ -6474,7 +6483,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="57">
-        <v>12078.18</v>
+        <v>1938.38</v>
       </c>
       <c r="H124">
         <f>_xlfn.XLOOKUP(A124,indice!A:A,indice!C:C)</f>
@@ -6483,133 +6492,133 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C125" s="57">
-        <v>6189335.3600000003</v>
+        <v>165635.67000000001</v>
       </c>
       <c r="D125" s="57">
-        <v>1702492.42</v>
+        <v>0</v>
       </c>
       <c r="E125" s="57">
-        <v>35056.15</v>
+        <v>0</v>
       </c>
       <c r="F125" s="57">
-        <v>1667436.27</v>
+        <v>0</v>
       </c>
       <c r="G125" s="57">
-        <v>7856771.6299999999</v>
-      </c>
-      <c r="H125" t="str">
+        <v>165635.67000000001</v>
+      </c>
+      <c r="H125">
         <f>_xlfn.XLOOKUP(A125,indice!A:A,indice!C:C)</f>
-        <v>S</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B126" t="s">
-        <v>133</v>
+        <v>259</v>
       </c>
       <c r="C126" s="57">
-        <v>1417589.96</v>
+        <v>1230560.1499999999</v>
       </c>
       <c r="D126" s="57">
-        <v>440681.78</v>
+        <v>0</v>
       </c>
       <c r="E126" s="57">
-        <v>142.19999999999999</v>
+        <v>0</v>
       </c>
       <c r="F126" s="57">
-        <v>440539.58</v>
+        <v>0</v>
       </c>
       <c r="G126" s="57">
-        <v>1858129.54</v>
+        <v>1230560.1499999999</v>
       </c>
       <c r="H126">
         <f>_xlfn.XLOOKUP(A126,indice!A:A,indice!C:C)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>263</v>
+        <v>446</v>
       </c>
       <c r="B127" t="s">
-        <v>135</v>
+        <v>447</v>
       </c>
       <c r="C127" s="57">
-        <v>157107.51</v>
+        <v>52578.18</v>
       </c>
       <c r="D127" s="57">
-        <v>49645.42</v>
+        <v>0</v>
       </c>
       <c r="E127" s="57">
         <v>0</v>
       </c>
       <c r="F127" s="57">
-        <v>49645.42</v>
+        <v>0</v>
       </c>
       <c r="G127" s="57">
-        <v>206752.93</v>
+        <v>52578.18</v>
       </c>
       <c r="H127">
         <f>_xlfn.XLOOKUP(A127,indice!A:A,indice!C:C)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>261</v>
       </c>
       <c r="C128" s="57">
-        <v>211406.64</v>
+        <v>9629371.7200000007</v>
       </c>
       <c r="D128" s="57">
-        <v>65928.92</v>
+        <v>1941095.6</v>
       </c>
       <c r="E128" s="57">
-        <v>1630.74</v>
+        <v>41379.31</v>
       </c>
       <c r="F128" s="57">
-        <v>64298.18</v>
+        <v>1899716.29</v>
       </c>
       <c r="G128" s="57">
-        <v>275704.82</v>
-      </c>
-      <c r="H128">
+        <v>11529088.01</v>
+      </c>
+      <c r="H128" t="str">
         <f>_xlfn.XLOOKUP(A128,indice!A:A,indice!C:C)</f>
-        <v>11</v>
+        <v>S</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B129" t="s">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="C129" s="57">
-        <v>178393.56</v>
+        <v>2347483.21</v>
       </c>
       <c r="D129" s="57">
-        <v>59464.52</v>
+        <v>470284.51</v>
       </c>
       <c r="E129" s="57">
-        <v>0</v>
+        <v>1182.93</v>
       </c>
       <c r="F129" s="57">
-        <v>59464.52</v>
+        <v>469101.58</v>
       </c>
       <c r="G129" s="57">
-        <v>237858.08</v>
+        <v>2816584.79</v>
       </c>
       <c r="H129">
         <f>_xlfn.XLOOKUP(A129,indice!A:A,indice!C:C)</f>
@@ -6618,25 +6627,25 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B130" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="C130" s="57">
-        <v>54270.77</v>
+        <v>257396.38</v>
       </c>
       <c r="D130" s="57">
-        <v>18490.3</v>
+        <v>49799.99</v>
       </c>
       <c r="E130" s="57">
-        <v>94.58</v>
+        <v>0</v>
       </c>
       <c r="F130" s="57">
-        <v>18395.72</v>
+        <v>49799.99</v>
       </c>
       <c r="G130" s="57">
-        <v>72666.490000000005</v>
+        <v>307196.37</v>
       </c>
       <c r="H130">
         <f>_xlfn.XLOOKUP(A130,indice!A:A,indice!C:C)</f>
@@ -6645,25 +6654,25 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B131" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="C131" s="57">
-        <v>153520.75</v>
+        <v>342667.92</v>
       </c>
       <c r="D131" s="57">
-        <v>47257.49</v>
+        <v>65656.570000000007</v>
       </c>
       <c r="E131" s="57">
-        <v>130.46</v>
+        <v>149.03</v>
       </c>
       <c r="F131" s="57">
-        <v>47127.03</v>
+        <v>65507.54</v>
       </c>
       <c r="G131" s="57">
-        <v>200647.78</v>
+        <v>408175.46</v>
       </c>
       <c r="H131">
         <f>_xlfn.XLOOKUP(A131,indice!A:A,indice!C:C)</f>
@@ -6672,25 +6681,25 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B132" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C132" s="57">
-        <v>15000</v>
+        <v>297322.59999999998</v>
       </c>
       <c r="D132" s="57">
-        <v>0</v>
+        <v>59464.52</v>
       </c>
       <c r="E132" s="57">
         <v>0</v>
       </c>
       <c r="F132" s="57">
-        <v>0</v>
+        <v>59464.52</v>
       </c>
       <c r="G132" s="57">
-        <v>15000</v>
+        <v>356787.12</v>
       </c>
       <c r="H132">
         <f>_xlfn.XLOOKUP(A132,indice!A:A,indice!C:C)</f>
@@ -6699,25 +6708,25 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="C133" s="57">
-        <v>71697.53</v>
+        <v>91230.16</v>
       </c>
       <c r="D133" s="57">
-        <v>12718.31</v>
+        <v>18411.52</v>
       </c>
       <c r="E133" s="57">
-        <v>0</v>
+        <v>312.74</v>
       </c>
       <c r="F133" s="57">
-        <v>12718.31</v>
+        <v>18098.78</v>
       </c>
       <c r="G133" s="57">
-        <v>84415.84</v>
+        <v>109328.94</v>
       </c>
       <c r="H133">
         <f>_xlfn.XLOOKUP(A133,indice!A:A,indice!C:C)</f>
@@ -6726,25 +6735,25 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B134" t="s">
-        <v>273</v>
+        <v>64</v>
       </c>
       <c r="C134" s="57">
-        <v>14717.36</v>
+        <v>251128.95999999999</v>
       </c>
       <c r="D134" s="57">
-        <v>11809.86</v>
+        <v>49276.4</v>
       </c>
       <c r="E134" s="57">
-        <v>0</v>
+        <v>358.46</v>
       </c>
       <c r="F134" s="57">
-        <v>11809.86</v>
+        <v>48917.94</v>
       </c>
       <c r="G134" s="57">
-        <v>26527.22</v>
+        <v>300046.90000000002</v>
       </c>
       <c r="H134">
         <f>_xlfn.XLOOKUP(A134,indice!A:A,indice!C:C)</f>
@@ -6753,25 +6762,25 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B135" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C135" s="57">
-        <v>3500</v>
+        <v>15000</v>
       </c>
       <c r="D135" s="57">
-        <v>0</v>
+        <v>19478.919999999998</v>
       </c>
       <c r="E135" s="57">
         <v>0</v>
       </c>
       <c r="F135" s="57">
-        <v>0</v>
+        <v>19478.919999999998</v>
       </c>
       <c r="G135" s="57">
-        <v>3500</v>
+        <v>34478.92</v>
       </c>
       <c r="H135">
         <f>_xlfn.XLOOKUP(A135,indice!A:A,indice!C:C)</f>
@@ -6780,25 +6789,25 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B136" t="s">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="C136" s="57">
-        <v>388.54</v>
+        <v>96434.15</v>
       </c>
       <c r="D136" s="57">
-        <v>0</v>
+        <v>13418.31</v>
       </c>
       <c r="E136" s="57">
         <v>0</v>
       </c>
       <c r="F136" s="57">
-        <v>0</v>
+        <v>13418.31</v>
       </c>
       <c r="G136" s="57">
-        <v>388.54</v>
+        <v>109852.46</v>
       </c>
       <c r="H136">
         <f>_xlfn.XLOOKUP(A136,indice!A:A,indice!C:C)</f>
@@ -6807,25 +6816,25 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B137" t="s">
-        <v>143</v>
+        <v>273</v>
       </c>
       <c r="C137" s="57">
-        <v>425542.08</v>
+        <v>41429.69</v>
       </c>
       <c r="D137" s="57">
-        <v>46667.14</v>
+        <v>13834.04</v>
       </c>
       <c r="E137" s="57">
         <v>0</v>
       </c>
       <c r="F137" s="57">
-        <v>46667.14</v>
+        <v>13834.04</v>
       </c>
       <c r="G137" s="57">
-        <v>472209.22</v>
+        <v>55263.73</v>
       </c>
       <c r="H137">
         <f>_xlfn.XLOOKUP(A137,indice!A:A,indice!C:C)</f>
@@ -6834,25 +6843,25 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="C138" s="57">
-        <v>1829</v>
+        <v>3500</v>
       </c>
       <c r="D138" s="57">
-        <v>299.60000000000002</v>
+        <v>0</v>
       </c>
       <c r="E138" s="57">
         <v>0</v>
       </c>
       <c r="F138" s="57">
-        <v>299.60000000000002</v>
+        <v>0</v>
       </c>
       <c r="G138" s="57">
-        <v>2128.6</v>
+        <v>3500</v>
       </c>
       <c r="H138">
         <f>_xlfn.XLOOKUP(A138,indice!A:A,indice!C:C)</f>
@@ -6861,25 +6870,25 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>280</v>
+        <v>524</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>525</v>
       </c>
       <c r="C139" s="57">
-        <v>2314</v>
+        <v>0</v>
       </c>
       <c r="D139" s="57">
-        <v>5000</v>
+        <v>1845</v>
       </c>
       <c r="E139" s="57">
         <v>0</v>
       </c>
       <c r="F139" s="57">
-        <v>5000</v>
+        <v>1845</v>
       </c>
       <c r="G139" s="57">
-        <v>7314</v>
+        <v>1845</v>
       </c>
       <c r="H139">
         <f>_xlfn.XLOOKUP(A139,indice!A:A,indice!C:C)</f>
@@ -6888,25 +6897,25 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B140" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C140" s="57">
-        <v>3067.36</v>
+        <v>388.54</v>
       </c>
       <c r="D140" s="57">
-        <v>9514.6299999999992</v>
+        <v>1167</v>
       </c>
       <c r="E140" s="57">
         <v>0</v>
       </c>
       <c r="F140" s="57">
-        <v>9514.6299999999992</v>
+        <v>1167</v>
       </c>
       <c r="G140" s="57">
-        <v>12581.99</v>
+        <v>1555.54</v>
       </c>
       <c r="H140">
         <f>_xlfn.XLOOKUP(A140,indice!A:A,indice!C:C)</f>
@@ -6915,25 +6924,25 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B141" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C141" s="57">
-        <v>264.95999999999998</v>
+        <v>546096.56000000006</v>
       </c>
       <c r="D141" s="57">
-        <v>28</v>
+        <v>88227.75</v>
       </c>
       <c r="E141" s="57">
         <v>0</v>
       </c>
       <c r="F141" s="57">
-        <v>28</v>
+        <v>88227.75</v>
       </c>
       <c r="G141" s="57">
-        <v>292.95999999999998</v>
+        <v>634324.31000000006</v>
       </c>
       <c r="H141">
         <f>_xlfn.XLOOKUP(A141,indice!A:A,indice!C:C)</f>
@@ -6942,25 +6951,25 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B142" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C142" s="57">
-        <v>1643877.14</v>
+        <v>4564.1000000000004</v>
       </c>
       <c r="D142" s="57">
-        <v>562591.37</v>
+        <v>1914.7</v>
       </c>
       <c r="E142" s="57">
-        <v>914.4</v>
+        <v>0</v>
       </c>
       <c r="F142" s="57">
-        <v>561676.97</v>
+        <v>1914.7</v>
       </c>
       <c r="G142" s="57">
-        <v>2205554.11</v>
+        <v>6478.8</v>
       </c>
       <c r="H142">
         <f>_xlfn.XLOOKUP(A142,indice!A:A,indice!C:C)</f>
@@ -6969,13 +6978,13 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B143" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C143" s="57">
-        <v>1224</v>
+        <v>12064</v>
       </c>
       <c r="D143" s="57">
         <v>0</v>
@@ -6987,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="G143" s="57">
-        <v>1224</v>
+        <v>12064</v>
       </c>
       <c r="H143">
         <f>_xlfn.XLOOKUP(A143,indice!A:A,indice!C:C)</f>
@@ -6996,25 +7005,25 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B144" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C144" s="57">
-        <v>8591.66</v>
+        <v>13950.66</v>
       </c>
       <c r="D144" s="57">
-        <v>2863.88</v>
+        <v>0</v>
       </c>
       <c r="E144" s="57">
         <v>0</v>
       </c>
       <c r="F144" s="57">
-        <v>2863.88</v>
+        <v>0</v>
       </c>
       <c r="G144" s="57">
-        <v>11455.54</v>
+        <v>13950.66</v>
       </c>
       <c r="H144">
         <f>_xlfn.XLOOKUP(A144,indice!A:A,indice!C:C)</f>
@@ -7023,25 +7032,25 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B145" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C145" s="57">
-        <v>20657.3</v>
+        <v>292.95999999999998</v>
       </c>
       <c r="D145" s="57">
-        <v>0</v>
+        <v>668.56</v>
       </c>
       <c r="E145" s="57">
         <v>0</v>
       </c>
       <c r="F145" s="57">
-        <v>0</v>
+        <v>668.56</v>
       </c>
       <c r="G145" s="57">
-        <v>20657.3</v>
+        <v>961.52</v>
       </c>
       <c r="H145">
         <f>_xlfn.XLOOKUP(A145,indice!A:A,indice!C:C)</f>
@@ -7050,25 +7059,25 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B146" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C146" s="57">
-        <v>8861.86</v>
+        <v>0</v>
       </c>
       <c r="D146" s="57">
-        <v>3374.56</v>
+        <v>490</v>
       </c>
       <c r="E146" s="57">
-        <v>312.14999999999998</v>
+        <v>0</v>
       </c>
       <c r="F146" s="57">
-        <v>3062.41</v>
+        <v>490</v>
       </c>
       <c r="G146" s="57">
-        <v>11924.27</v>
+        <v>490</v>
       </c>
       <c r="H146">
         <f>_xlfn.XLOOKUP(A146,indice!A:A,indice!C:C)</f>
@@ -7077,25 +7086,25 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B147" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C147" s="57">
-        <v>6806.25</v>
+        <v>2759135.32</v>
       </c>
       <c r="D147" s="57">
-        <v>0</v>
+        <v>530140.62</v>
       </c>
       <c r="E147" s="57">
-        <v>0</v>
+        <v>1175.95</v>
       </c>
       <c r="F147" s="57">
-        <v>0</v>
+        <v>528964.67000000004</v>
       </c>
       <c r="G147" s="57">
-        <v>6806.25</v>
+        <v>3288099.99</v>
       </c>
       <c r="H147">
         <f>_xlfn.XLOOKUP(A147,indice!A:A,indice!C:C)</f>
@@ -7104,25 +7113,25 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B148" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C148" s="57">
-        <v>538.94000000000005</v>
+        <v>1602.23</v>
       </c>
       <c r="D148" s="57">
-        <v>184.84</v>
+        <v>776.92</v>
       </c>
       <c r="E148" s="57">
         <v>0</v>
       </c>
       <c r="F148" s="57">
-        <v>184.84</v>
+        <v>776.92</v>
       </c>
       <c r="G148" s="57">
-        <v>723.78</v>
+        <v>2379.15</v>
       </c>
       <c r="H148">
         <f>_xlfn.XLOOKUP(A148,indice!A:A,indice!C:C)</f>
@@ -7131,25 +7140,25 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B149" t="s">
-        <v>169</v>
+        <v>288</v>
       </c>
       <c r="C149" s="57">
-        <v>42389.23</v>
+        <v>14401.62</v>
       </c>
       <c r="D149" s="57">
-        <v>8737.82</v>
+        <v>1137.83</v>
       </c>
       <c r="E149" s="57">
         <v>0</v>
       </c>
       <c r="F149" s="57">
-        <v>8737.82</v>
+        <v>1137.83</v>
       </c>
       <c r="G149" s="57">
-        <v>51127.05</v>
+        <v>15539.45</v>
       </c>
       <c r="H149">
         <f>_xlfn.XLOOKUP(A149,indice!A:A,indice!C:C)</f>
@@ -7158,25 +7167,25 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B150" t="s">
-        <v>295</v>
+        <v>161</v>
       </c>
       <c r="C150" s="57">
-        <v>764.63</v>
+        <v>20657.3</v>
       </c>
       <c r="D150" s="57">
-        <v>512.39</v>
+        <v>2463.1799999999998</v>
       </c>
       <c r="E150" s="57">
         <v>0</v>
       </c>
       <c r="F150" s="57">
-        <v>512.39</v>
+        <v>2463.1799999999998</v>
       </c>
       <c r="G150" s="57">
-        <v>1277.02</v>
+        <v>23120.48</v>
       </c>
       <c r="H150">
         <f>_xlfn.XLOOKUP(A150,indice!A:A,indice!C:C)</f>
@@ -7185,25 +7194,25 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B151" t="s">
-        <v>297</v>
+        <v>163</v>
       </c>
       <c r="C151" s="57">
-        <v>33150.76</v>
+        <v>14422.96</v>
       </c>
       <c r="D151" s="57">
-        <v>5452.82</v>
+        <v>2292.4899999999998</v>
       </c>
       <c r="E151" s="57">
-        <v>0</v>
+        <v>212.06</v>
       </c>
       <c r="F151" s="57">
-        <v>5452.82</v>
+        <v>2080.4299999999998</v>
       </c>
       <c r="G151" s="57">
-        <v>38603.58</v>
+        <v>16503.39</v>
       </c>
       <c r="H151">
         <f>_xlfn.XLOOKUP(A151,indice!A:A,indice!C:C)</f>
@@ -7212,25 +7221,25 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B152" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C152" s="57">
-        <v>402.72</v>
+        <v>6806.25</v>
       </c>
       <c r="D152" s="57">
-        <v>321.64</v>
+        <v>0</v>
       </c>
       <c r="E152" s="57">
         <v>0</v>
       </c>
       <c r="F152" s="57">
-        <v>321.64</v>
+        <v>0</v>
       </c>
       <c r="G152" s="57">
-        <v>724.36</v>
+        <v>6806.25</v>
       </c>
       <c r="H152">
         <f>_xlfn.XLOOKUP(A152,indice!A:A,indice!C:C)</f>
@@ -7239,25 +7248,25 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B153" t="s">
-        <v>300</v>
+        <v>167</v>
       </c>
       <c r="C153" s="57">
-        <v>210616.18</v>
+        <v>7388.62</v>
       </c>
       <c r="D153" s="57">
-        <v>247.5</v>
+        <v>6664.84</v>
       </c>
       <c r="E153" s="57">
         <v>0</v>
       </c>
       <c r="F153" s="57">
-        <v>247.5</v>
+        <v>6664.84</v>
       </c>
       <c r="G153" s="57">
-        <v>210863.68</v>
+        <v>14053.46</v>
       </c>
       <c r="H153">
         <f>_xlfn.XLOOKUP(A153,indice!A:A,indice!C:C)</f>
@@ -7266,25 +7275,25 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B154" t="s">
-        <v>302</v>
+        <v>169</v>
       </c>
       <c r="C154" s="57">
-        <v>5287.65</v>
+        <v>105493.99</v>
       </c>
       <c r="D154" s="57">
-        <v>0</v>
+        <v>3607.62</v>
       </c>
       <c r="E154" s="57">
         <v>0</v>
       </c>
       <c r="F154" s="57">
-        <v>0</v>
+        <v>3607.62</v>
       </c>
       <c r="G154" s="57">
-        <v>5287.65</v>
+        <v>109101.61</v>
       </c>
       <c r="H154">
         <f>_xlfn.XLOOKUP(A154,indice!A:A,indice!C:C)</f>
@@ -7293,25 +7302,25 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B155" t="s">
-        <v>173</v>
+        <v>295</v>
       </c>
       <c r="C155" s="57">
-        <v>18229.18</v>
+        <v>2185.7199999999998</v>
       </c>
       <c r="D155" s="57">
-        <v>4138.33</v>
+        <v>791.75</v>
       </c>
       <c r="E155" s="57">
         <v>0</v>
       </c>
       <c r="F155" s="57">
-        <v>4138.33</v>
+        <v>791.75</v>
       </c>
       <c r="G155" s="57">
-        <v>22367.51</v>
+        <v>2977.47</v>
       </c>
       <c r="H155">
         <f>_xlfn.XLOOKUP(A155,indice!A:A,indice!C:C)</f>
@@ -7320,25 +7329,25 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B156" t="s">
-        <v>175</v>
+        <v>297</v>
       </c>
       <c r="C156" s="57">
-        <v>144984.1</v>
+        <v>41999.59</v>
       </c>
       <c r="D156" s="57">
-        <v>21684.17</v>
+        <v>55412.01</v>
       </c>
       <c r="E156" s="57">
         <v>0</v>
       </c>
       <c r="F156" s="57">
-        <v>21684.17</v>
+        <v>55412.01</v>
       </c>
       <c r="G156" s="57">
-        <v>166668.26999999999</v>
+        <v>97411.6</v>
       </c>
       <c r="H156">
         <f>_xlfn.XLOOKUP(A156,indice!A:A,indice!C:C)</f>
@@ -7347,25 +7356,25 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B157" t="s">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="C157" s="57">
-        <v>28668.7</v>
+        <v>21755.65</v>
       </c>
       <c r="D157" s="57">
-        <v>29202.15</v>
+        <v>69987.789999999994</v>
       </c>
       <c r="E157" s="57">
         <v>0</v>
       </c>
       <c r="F157" s="57">
-        <v>29202.15</v>
+        <v>69987.789999999994</v>
       </c>
       <c r="G157" s="57">
-        <v>57870.85</v>
+        <v>91743.44</v>
       </c>
       <c r="H157">
         <f>_xlfn.XLOOKUP(A157,indice!A:A,indice!C:C)</f>
@@ -7374,25 +7383,25 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B158" t="s">
-        <v>238</v>
+        <v>300</v>
       </c>
       <c r="C158" s="57">
-        <v>969.4</v>
+        <v>211469.93</v>
       </c>
       <c r="D158" s="57">
-        <v>0</v>
+        <v>273.82</v>
       </c>
       <c r="E158" s="57">
         <v>0</v>
       </c>
       <c r="F158" s="57">
-        <v>0</v>
+        <v>273.82</v>
       </c>
       <c r="G158" s="57">
-        <v>969.4</v>
+        <v>211743.75</v>
       </c>
       <c r="H158">
         <f>_xlfn.XLOOKUP(A158,indice!A:A,indice!C:C)</f>
@@ -7401,25 +7410,25 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B159" t="s">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="C159" s="57">
-        <v>21638.19</v>
+        <v>5287.65</v>
       </c>
       <c r="D159" s="57">
-        <v>9192.99</v>
+        <v>0</v>
       </c>
       <c r="E159" s="57">
         <v>0</v>
       </c>
       <c r="F159" s="57">
-        <v>9192.99</v>
+        <v>0</v>
       </c>
       <c r="G159" s="57">
-        <v>30831.18</v>
+        <v>5287.65</v>
       </c>
       <c r="H159">
         <f>_xlfn.XLOOKUP(A159,indice!A:A,indice!C:C)</f>
@@ -7428,25 +7437,25 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B160" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C160" s="57">
-        <v>670.7</v>
+        <v>28641.74</v>
       </c>
       <c r="D160" s="57">
-        <v>361.86</v>
+        <v>6738.29</v>
       </c>
       <c r="E160" s="57">
         <v>0</v>
       </c>
       <c r="F160" s="57">
-        <v>361.86</v>
+        <v>6738.29</v>
       </c>
       <c r="G160" s="57">
-        <v>1032.56</v>
+        <v>35380.03</v>
       </c>
       <c r="H160">
         <f>_xlfn.XLOOKUP(A160,indice!A:A,indice!C:C)</f>
@@ -7455,25 +7464,25 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B161" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="C161" s="57">
-        <v>81159.8</v>
+        <v>187210.46</v>
       </c>
       <c r="D161" s="57">
-        <v>26964.39</v>
+        <v>23576.63</v>
       </c>
       <c r="E161" s="57">
         <v>0</v>
       </c>
       <c r="F161" s="57">
-        <v>26964.39</v>
+        <v>23576.63</v>
       </c>
       <c r="G161" s="57">
-        <v>108124.19</v>
+        <v>210787.09</v>
       </c>
       <c r="H161">
         <f>_xlfn.XLOOKUP(A161,indice!A:A,indice!C:C)</f>
@@ -7482,25 +7491,25 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B162" t="s">
-        <v>195</v>
+        <v>306</v>
       </c>
       <c r="C162" s="57">
-        <v>866.18</v>
+        <v>74152.149999999994</v>
       </c>
       <c r="D162" s="57">
-        <v>325.51</v>
+        <v>15608.95</v>
       </c>
       <c r="E162" s="57">
         <v>0</v>
       </c>
       <c r="F162" s="57">
-        <v>325.51</v>
+        <v>15608.95</v>
       </c>
       <c r="G162" s="57">
-        <v>1191.69</v>
+        <v>89761.1</v>
       </c>
       <c r="H162">
         <f>_xlfn.XLOOKUP(A162,indice!A:A,indice!C:C)</f>
@@ -7509,25 +7518,25 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B163" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="C163" s="57">
-        <v>53587.64</v>
+        <v>969.4</v>
       </c>
       <c r="D163" s="57">
-        <v>6600</v>
+        <v>1084.55</v>
       </c>
       <c r="E163" s="57">
         <v>0</v>
       </c>
       <c r="F163" s="57">
-        <v>6600</v>
+        <v>1084.55</v>
       </c>
       <c r="G163" s="57">
-        <v>60187.64</v>
+        <v>2053.9499999999998</v>
       </c>
       <c r="H163">
         <f>_xlfn.XLOOKUP(A163,indice!A:A,indice!C:C)</f>
@@ -7536,25 +7545,25 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>316</v>
+        <v>474</v>
       </c>
       <c r="B164" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="C164" s="57">
-        <v>-215778.01</v>
+        <v>46</v>
       </c>
       <c r="D164" s="57">
-        <v>261.22000000000003</v>
+        <v>0</v>
       </c>
       <c r="E164" s="57">
-        <v>31831.62</v>
+        <v>0</v>
       </c>
       <c r="F164" s="57">
-        <v>-31570.400000000001</v>
+        <v>0</v>
       </c>
       <c r="G164" s="57">
-        <v>-247348.41</v>
+        <v>46</v>
       </c>
       <c r="H164">
         <f>_xlfn.XLOOKUP(A164,indice!A:A,indice!C:C)</f>
@@ -7563,25 +7572,25 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B165" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C165" s="57">
-        <v>48013.68</v>
+        <v>31542.03</v>
       </c>
       <c r="D165" s="57">
-        <v>7795.59</v>
+        <v>3084.71</v>
       </c>
       <c r="E165" s="57">
         <v>0</v>
       </c>
       <c r="F165" s="57">
-        <v>7795.59</v>
+        <v>3084.71</v>
       </c>
       <c r="G165" s="57">
-        <v>55809.27</v>
+        <v>34626.74</v>
       </c>
       <c r="H165">
         <f>_xlfn.XLOOKUP(A165,indice!A:A,indice!C:C)</f>
@@ -7590,25 +7599,25 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B166" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C166" s="57">
-        <v>89450.41</v>
+        <v>1612.74</v>
       </c>
       <c r="D166" s="57">
-        <v>27129.9</v>
+        <v>1410</v>
       </c>
       <c r="E166" s="57">
         <v>0</v>
       </c>
       <c r="F166" s="57">
-        <v>27129.9</v>
+        <v>1410</v>
       </c>
       <c r="G166" s="57">
-        <v>116580.31</v>
+        <v>3022.74</v>
       </c>
       <c r="H166">
         <f>_xlfn.XLOOKUP(A166,indice!A:A,indice!C:C)</f>
@@ -7617,25 +7626,25 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B167" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C167" s="57">
-        <v>6808.2</v>
+        <v>106950.18</v>
       </c>
       <c r="D167" s="57">
-        <v>1621</v>
+        <v>27058.12</v>
       </c>
       <c r="E167" s="57">
-        <v>0</v>
+        <v>6136.58</v>
       </c>
       <c r="F167" s="57">
-        <v>1621</v>
+        <v>20921.54</v>
       </c>
       <c r="G167" s="57">
-        <v>8429.2000000000007</v>
+        <v>127871.72</v>
       </c>
       <c r="H167">
         <f>_xlfn.XLOOKUP(A167,indice!A:A,indice!C:C)</f>
@@ -7644,25 +7653,25 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B168" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C168" s="57">
-        <v>20639.71</v>
+        <v>2958.84</v>
       </c>
       <c r="D168" s="57">
-        <v>4160</v>
+        <v>235.25</v>
       </c>
       <c r="E168" s="57">
         <v>0</v>
       </c>
       <c r="F168" s="57">
-        <v>4160</v>
+        <v>235.25</v>
       </c>
       <c r="G168" s="57">
-        <v>24799.71</v>
+        <v>3194.09</v>
       </c>
       <c r="H168">
         <f>_xlfn.XLOOKUP(A168,indice!A:A,indice!C:C)</f>
@@ -7671,25 +7680,25 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B169" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="C169" s="57">
-        <v>2150.4499999999998</v>
+        <v>66687.64</v>
       </c>
       <c r="D169" s="57">
-        <v>0</v>
+        <v>62615.73</v>
       </c>
       <c r="E169" s="57">
         <v>0</v>
       </c>
       <c r="F169" s="57">
-        <v>0</v>
+        <v>62615.73</v>
       </c>
       <c r="G169" s="57">
-        <v>2150.4499999999998</v>
+        <v>129303.37</v>
       </c>
       <c r="H169">
         <f>_xlfn.XLOOKUP(A169,indice!A:A,indice!C:C)</f>
@@ -7698,25 +7707,25 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B170" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C170" s="57">
-        <v>17812.8</v>
+        <v>-276437.55</v>
       </c>
       <c r="D170" s="57">
-        <v>4589.3</v>
+        <v>289.35000000000002</v>
       </c>
       <c r="E170" s="57">
-        <v>0</v>
+        <v>31851.56</v>
       </c>
       <c r="F170" s="57">
-        <v>4589.3</v>
+        <v>-31562.21</v>
       </c>
       <c r="G170" s="57">
-        <v>22402.1</v>
+        <v>-307999.76</v>
       </c>
       <c r="H170">
         <f>_xlfn.XLOOKUP(A170,indice!A:A,indice!C:C)</f>
@@ -7725,25 +7734,25 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B171" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C171" s="57">
-        <v>30805.38</v>
+        <v>64670.5</v>
       </c>
       <c r="D171" s="57">
-        <v>5879.7</v>
+        <v>7747.02</v>
       </c>
       <c r="E171" s="57">
         <v>0</v>
       </c>
       <c r="F171" s="57">
-        <v>5879.7</v>
+        <v>7747.02</v>
       </c>
       <c r="G171" s="57">
-        <v>36685.08</v>
+        <v>72417.52</v>
       </c>
       <c r="H171">
         <f>_xlfn.XLOOKUP(A171,indice!A:A,indice!C:C)</f>
@@ -7752,25 +7761,25 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B172" t="s">
-        <v>325</v>
+        <v>203</v>
       </c>
       <c r="C172" s="57">
-        <v>161871.9</v>
+        <v>143710.21</v>
       </c>
       <c r="D172" s="57">
-        <v>1700.6</v>
+        <v>24510.18</v>
       </c>
       <c r="E172" s="57">
         <v>0</v>
       </c>
       <c r="F172" s="57">
-        <v>1700.6</v>
+        <v>24510.18</v>
       </c>
       <c r="G172" s="57">
-        <v>163572.5</v>
+        <v>168220.39</v>
       </c>
       <c r="H172">
         <f>_xlfn.XLOOKUP(A172,indice!A:A,indice!C:C)</f>
@@ -7779,25 +7788,25 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B173" t="s">
-        <v>327</v>
+        <v>205</v>
       </c>
       <c r="C173" s="57">
-        <v>9550.7000000000007</v>
+        <v>9726</v>
       </c>
       <c r="D173" s="57">
-        <v>713.19</v>
+        <v>1647.37</v>
       </c>
       <c r="E173" s="57">
         <v>0</v>
       </c>
       <c r="F173" s="57">
-        <v>713.19</v>
+        <v>1647.37</v>
       </c>
       <c r="G173" s="57">
-        <v>10263.89</v>
+        <v>11373.37</v>
       </c>
       <c r="H173">
         <f>_xlfn.XLOOKUP(A173,indice!A:A,indice!C:C)</f>
@@ -7806,25 +7815,25 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B174" t="s">
-        <v>329</v>
+        <v>207</v>
       </c>
       <c r="C174" s="57">
-        <v>126155.22</v>
+        <v>33525.46</v>
       </c>
       <c r="D174" s="57">
-        <v>25786.799999999999</v>
+        <v>3147.6</v>
       </c>
       <c r="E174" s="57">
         <v>0</v>
       </c>
       <c r="F174" s="57">
-        <v>25786.799999999999</v>
+        <v>3147.6</v>
       </c>
       <c r="G174" s="57">
-        <v>151942.01999999999</v>
+        <v>36673.06</v>
       </c>
       <c r="H174">
         <f>_xlfn.XLOOKUP(A174,indice!A:A,indice!C:C)</f>
@@ -7833,25 +7842,25 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B175" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C175" s="57">
-        <v>92998.11</v>
+        <v>2150.4499999999998</v>
       </c>
       <c r="D175" s="57">
-        <v>27995.81</v>
+        <v>0</v>
       </c>
       <c r="E175" s="57">
         <v>0</v>
       </c>
       <c r="F175" s="57">
-        <v>27995.81</v>
+        <v>0</v>
       </c>
       <c r="G175" s="57">
-        <v>120993.92</v>
+        <v>2150.4499999999998</v>
       </c>
       <c r="H175">
         <f>_xlfn.XLOOKUP(A175,indice!A:A,indice!C:C)</f>
@@ -7860,25 +7869,25 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>475</v>
+        <v>322</v>
       </c>
       <c r="B176" t="s">
-        <v>476</v>
+        <v>211</v>
       </c>
       <c r="C176" s="57">
-        <v>43319.92</v>
+        <v>26679.86</v>
       </c>
       <c r="D176" s="57">
-        <v>0</v>
+        <v>4401.42</v>
       </c>
       <c r="E176" s="57">
         <v>0</v>
       </c>
       <c r="F176" s="57">
-        <v>0</v>
+        <v>4401.42</v>
       </c>
       <c r="G176" s="57">
-        <v>43319.92</v>
+        <v>31081.279999999999</v>
       </c>
       <c r="H176">
         <f>_xlfn.XLOOKUP(A176,indice!A:A,indice!C:C)</f>
@@ -7887,25 +7896,25 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B177" t="s">
-        <v>332</v>
+        <v>213</v>
       </c>
       <c r="C177" s="57">
-        <v>437137.82</v>
+        <v>44517.87</v>
       </c>
       <c r="D177" s="57">
-        <v>144597.12</v>
+        <v>5772.96</v>
       </c>
       <c r="E177" s="57">
         <v>0</v>
       </c>
       <c r="F177" s="57">
-        <v>144597.12</v>
+        <v>5772.96</v>
       </c>
       <c r="G177" s="57">
-        <v>581734.93999999994</v>
+        <v>50290.83</v>
       </c>
       <c r="H177">
         <f>_xlfn.XLOOKUP(A177,indice!A:A,indice!C:C)</f>
@@ -7914,25 +7923,25 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B178" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C178" s="57">
-        <v>273846.84000000003</v>
+        <v>164372.5</v>
       </c>
       <c r="D178" s="57">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E178" s="57">
         <v>0</v>
       </c>
       <c r="F178" s="57">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="G178" s="57">
-        <v>273846.84000000003</v>
+        <v>165672.5</v>
       </c>
       <c r="H178">
         <f>_xlfn.XLOOKUP(A178,indice!A:A,indice!C:C)</f>
@@ -7941,241 +7950,241 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B179" t="s">
-        <v>18</v>
+        <v>327</v>
       </c>
       <c r="C179" s="57">
-        <v>3352863.13</v>
+        <v>11708.98</v>
       </c>
       <c r="D179" s="57">
-        <v>1474272.07</v>
+        <v>3387.33</v>
       </c>
       <c r="E179" s="57">
-        <v>928211.63</v>
+        <v>0</v>
       </c>
       <c r="F179" s="57">
-        <v>546060.43999999994</v>
+        <v>3387.33</v>
       </c>
       <c r="G179" s="57">
-        <v>3898923.57</v>
-      </c>
-      <c r="H179" t="str">
+        <v>15096.31</v>
+      </c>
+      <c r="H179">
         <f>_xlfn.XLOOKUP(A179,indice!A:A,indice!C:C)</f>
-        <v>S</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>500</v>
+        <v>328</v>
       </c>
       <c r="B180" t="s">
-        <v>501</v>
+        <v>329</v>
       </c>
       <c r="C180" s="57">
-        <v>282457.75</v>
+        <v>175758.84</v>
       </c>
       <c r="D180" s="57">
-        <v>0</v>
+        <v>9888.39</v>
       </c>
       <c r="E180" s="57">
         <v>0</v>
       </c>
       <c r="F180" s="57">
-        <v>0</v>
+        <v>9888.39</v>
       </c>
       <c r="G180" s="57">
-        <v>282457.75</v>
+        <v>185647.23</v>
       </c>
       <c r="H180">
         <f>_xlfn.XLOOKUP(A180,indice!A:A,indice!C:C)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B181" t="s">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c r="C181" s="57">
-        <v>4577337.5599999996</v>
+        <v>151051.97</v>
       </c>
       <c r="D181" s="57">
-        <v>1462049.32</v>
+        <v>29237.14</v>
       </c>
       <c r="E181" s="57">
-        <v>1748.25</v>
+        <v>0</v>
       </c>
       <c r="F181" s="57">
-        <v>1460301.07</v>
+        <v>29237.14</v>
       </c>
       <c r="G181" s="57">
-        <v>6037638.6299999999</v>
+        <v>180289.11</v>
       </c>
       <c r="H181">
         <f>_xlfn.XLOOKUP(A181,indice!A:A,indice!C:C)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>338</v>
+        <v>475</v>
       </c>
       <c r="B182" t="s">
-        <v>339</v>
+        <v>476</v>
       </c>
       <c r="C182" s="57">
-        <v>0</v>
+        <v>43319.92</v>
       </c>
       <c r="D182" s="57">
-        <v>11809</v>
+        <v>982.23</v>
       </c>
       <c r="E182" s="57">
         <v>0</v>
       </c>
       <c r="F182" s="57">
-        <v>11809</v>
+        <v>982.23</v>
       </c>
       <c r="G182" s="57">
-        <v>11809</v>
+        <v>44302.15</v>
       </c>
       <c r="H182">
         <f>_xlfn.XLOOKUP(A182,indice!A:A,indice!C:C)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>340</v>
+        <v>423</v>
       </c>
       <c r="B183" t="s">
-        <v>341</v>
+        <v>424</v>
       </c>
       <c r="C183" s="57">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="D183" s="57">
-        <v>0</v>
+        <v>2276.0300000000002</v>
       </c>
       <c r="E183" s="57">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F183" s="57">
-        <v>-0.03</v>
+        <v>2276.0300000000002</v>
       </c>
       <c r="G183" s="57">
-        <v>-0.05</v>
+        <v>2276.0300000000002</v>
       </c>
       <c r="H183">
         <f>_xlfn.XLOOKUP(A183,indice!A:A,indice!C:C)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B184" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C184" s="57">
-        <v>-209.24</v>
+        <v>726441.97</v>
       </c>
       <c r="D184" s="57">
-        <v>413.75</v>
+        <v>177609.69</v>
       </c>
       <c r="E184" s="57">
-        <v>27.93</v>
+        <v>0</v>
       </c>
       <c r="F184" s="57">
-        <v>385.82</v>
+        <v>177609.69</v>
       </c>
       <c r="G184" s="57">
-        <v>176.58</v>
+        <v>904051.66</v>
       </c>
       <c r="H184">
         <f>_xlfn.XLOOKUP(A184,indice!A:A,indice!C:C)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="B185" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C185" s="57">
-        <v>-17192.93</v>
+        <v>273846.84000000003</v>
       </c>
       <c r="D185" s="57">
         <v>0</v>
       </c>
       <c r="E185" s="57">
-        <v>5635.42</v>
+        <v>0</v>
       </c>
       <c r="F185" s="57">
-        <v>-5635.42</v>
+        <v>0</v>
       </c>
       <c r="G185" s="57">
-        <v>-22828.35</v>
+        <v>273846.84000000003</v>
       </c>
       <c r="H185">
         <f>_xlfn.XLOOKUP(A185,indice!A:A,indice!C:C)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>469</v>
+        <v>335</v>
       </c>
       <c r="B186" t="s">
-        <v>470</v>
+        <v>18</v>
       </c>
       <c r="C186" s="57">
-        <v>-420282.99</v>
+        <v>5552728.2400000002</v>
       </c>
       <c r="D186" s="57">
-        <v>0</v>
+        <v>1749475.76</v>
       </c>
       <c r="E186" s="57">
-        <v>0</v>
+        <v>7409.39</v>
       </c>
       <c r="F186" s="57">
-        <v>0</v>
+        <v>1742066.37</v>
       </c>
       <c r="G186" s="57">
-        <v>-420282.99</v>
-      </c>
-      <c r="H186">
+        <v>7294794.6100000003</v>
+      </c>
+      <c r="H186" t="str">
         <f>_xlfn.XLOOKUP(A186,indice!A:A,indice!C:C)</f>
-        <v>14</v>
+        <v>S</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="B187" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="C187" s="57">
-        <v>-1702347</v>
+        <v>282457.75</v>
       </c>
       <c r="D187" s="57">
         <v>0</v>
       </c>
       <c r="E187" s="57">
-        <v>920800</v>
+        <v>0</v>
       </c>
       <c r="F187" s="57">
-        <v>-920800</v>
+        <v>0</v>
       </c>
       <c r="G187" s="57">
-        <v>-2623147</v>
+        <v>282457.75</v>
       </c>
       <c r="H187">
         <f>_xlfn.XLOOKUP(A187,indice!A:A,indice!C:C)</f>
@@ -8184,25 +8193,25 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>517</v>
+        <v>336</v>
       </c>
       <c r="B188" t="s">
-        <v>518</v>
+        <v>337</v>
       </c>
       <c r="C188" s="57">
-        <v>633100</v>
+        <v>7424089.3399999999</v>
       </c>
       <c r="D188" s="57">
-        <v>0</v>
+        <v>1270675.76</v>
       </c>
       <c r="E188" s="57">
         <v>0</v>
       </c>
       <c r="F188" s="57">
-        <v>0</v>
+        <v>1270675.76</v>
       </c>
       <c r="G188" s="57">
-        <v>633100</v>
+        <v>8694765.0999999996</v>
       </c>
       <c r="H188">
         <f>_xlfn.XLOOKUP(A188,indice!A:A,indice!C:C)</f>
@@ -8211,40 +8220,40 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="B189" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C189" s="57">
-        <v>-3913506.48</v>
+        <v>11809</v>
       </c>
       <c r="D189" s="57">
-        <v>56094.17</v>
+        <v>0</v>
       </c>
       <c r="E189" s="57">
-        <v>554915.89</v>
+        <v>0</v>
       </c>
       <c r="F189" s="57">
-        <v>-498821.72</v>
+        <v>0</v>
       </c>
       <c r="G189" s="57">
-        <v>-4412328.2</v>
-      </c>
-      <c r="H189" t="str">
+        <v>11809</v>
+      </c>
+      <c r="H189">
         <f>_xlfn.XLOOKUP(A189,indice!A:A,indice!C:C)</f>
-        <v>S</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B190" t="s">
-        <v>56</v>
+        <v>341</v>
       </c>
       <c r="C190" s="57">
-        <v>13.05</v>
+        <v>-0.05</v>
       </c>
       <c r="D190" s="57">
         <v>0</v>
@@ -8256,76 +8265,76 @@
         <v>0</v>
       </c>
       <c r="G190" s="57">
-        <v>13.05</v>
+        <v>-0.05</v>
       </c>
       <c r="H190">
         <f>_xlfn.XLOOKUP(A190,indice!A:A,indice!C:C)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="B191" t="s">
-        <v>57</v>
+        <v>343</v>
       </c>
       <c r="C191" s="57">
-        <v>1176.8699999999999</v>
+        <v>113.82</v>
       </c>
       <c r="D191" s="57">
-        <v>1569.95</v>
+        <v>0</v>
       </c>
       <c r="E191" s="57">
-        <v>0</v>
+        <v>851.11</v>
       </c>
       <c r="F191" s="57">
-        <v>1569.95</v>
+        <v>-851.11</v>
       </c>
       <c r="G191" s="57">
-        <v>2746.82</v>
+        <v>-737.29</v>
       </c>
       <c r="H191">
         <f>_xlfn.XLOOKUP(A191,indice!A:A,indice!C:C)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B192" t="s">
-        <v>58</v>
+        <v>347</v>
       </c>
       <c r="C192" s="57">
-        <v>5523.6</v>
+        <v>-28611.63</v>
       </c>
       <c r="D192" s="57">
-        <v>7287.98</v>
+        <v>0</v>
       </c>
       <c r="E192" s="57">
-        <v>0</v>
+        <v>6558.28</v>
       </c>
       <c r="F192" s="57">
-        <v>7287.98</v>
+        <v>-6558.28</v>
       </c>
       <c r="G192" s="57">
-        <v>12811.58</v>
+        <v>-35169.910000000003</v>
       </c>
       <c r="H192">
         <f>_xlfn.XLOOKUP(A192,indice!A:A,indice!C:C)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>355</v>
+        <v>469</v>
       </c>
       <c r="B193" t="s">
-        <v>356</v>
+        <v>470</v>
       </c>
       <c r="C193" s="57">
-        <v>-293834.42</v>
+        <v>-420282.99</v>
       </c>
       <c r="D193" s="57">
         <v>0</v>
@@ -8337,115 +8346,115 @@
         <v>0</v>
       </c>
       <c r="G193" s="57">
-        <v>-293834.42</v>
+        <v>-420282.99</v>
       </c>
       <c r="H193">
         <f>_xlfn.XLOOKUP(A193,indice!A:A,indice!C:C)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>448</v>
+        <v>511</v>
       </c>
       <c r="B194" t="s">
-        <v>449</v>
+        <v>512</v>
       </c>
       <c r="C194" s="57">
-        <v>6196.51</v>
+        <v>-2623147</v>
       </c>
       <c r="D194" s="57">
-        <v>37044.959999999999</v>
+        <v>0</v>
       </c>
       <c r="E194" s="57">
-        <v>32863.4</v>
+        <v>0</v>
       </c>
       <c r="F194" s="57">
-        <v>4181.5600000000004</v>
+        <v>0</v>
       </c>
       <c r="G194" s="57">
-        <v>10378.07</v>
+        <v>-2623147</v>
       </c>
       <c r="H194">
         <f>_xlfn.XLOOKUP(A194,indice!A:A,indice!C:C)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>357</v>
+        <v>517</v>
       </c>
       <c r="B195" t="s">
-        <v>358</v>
+        <v>518</v>
       </c>
       <c r="C195" s="57">
-        <v>-3786885.13</v>
+        <v>906300</v>
       </c>
       <c r="D195" s="57">
-        <v>0</v>
+        <v>478800</v>
       </c>
       <c r="E195" s="57">
-        <v>429124.1</v>
+        <v>0</v>
       </c>
       <c r="F195" s="57">
-        <v>-429124.1</v>
+        <v>478800</v>
       </c>
       <c r="G195" s="57">
-        <v>-4216009.2300000004</v>
+        <v>1385100</v>
       </c>
       <c r="H195">
         <f>_xlfn.XLOOKUP(A195,indice!A:A,indice!C:C)</f>
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B196" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C196" s="57">
-        <v>1128.81</v>
+        <v>-4406726.9800000004</v>
       </c>
       <c r="D196" s="57">
-        <v>10191.280000000001</v>
+        <v>26093.06</v>
       </c>
       <c r="E196" s="57">
-        <v>0</v>
+        <v>4666.6099999999997</v>
       </c>
       <c r="F196" s="57">
-        <v>10191.280000000001</v>
+        <v>21426.45</v>
       </c>
       <c r="G196" s="57">
-        <v>11320.09</v>
-      </c>
-      <c r="H196">
+        <v>-4385300.53</v>
+      </c>
+      <c r="H196" t="str">
         <f>_xlfn.XLOOKUP(A196,indice!A:A,indice!C:C)</f>
-        <v>12</v>
+        <v>S</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B197" t="s">
-        <v>362</v>
+        <v>56</v>
       </c>
       <c r="C197" s="57">
-        <v>-94603.48</v>
+        <v>13.05</v>
       </c>
       <c r="D197" s="57">
-        <v>0</v>
+        <v>1217.7</v>
       </c>
       <c r="E197" s="57">
-        <v>92928.39</v>
+        <v>0</v>
       </c>
       <c r="F197" s="57">
-        <v>-92928.39</v>
+        <v>1217.7</v>
       </c>
       <c r="G197" s="57">
-        <v>-187531.87</v>
+        <v>1230.75</v>
       </c>
       <c r="H197">
         <f>_xlfn.XLOOKUP(A197,indice!A:A,indice!C:C)</f>
@@ -8454,13 +8463,13 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B198" t="s">
-        <v>364</v>
+        <v>57</v>
       </c>
       <c r="C198" s="57">
-        <v>78748.75</v>
+        <v>2784.41</v>
       </c>
       <c r="D198" s="57">
         <v>0</v>
@@ -8472,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="G198" s="57">
-        <v>78748.75</v>
+        <v>2784.41</v>
       </c>
       <c r="H198">
         <f>_xlfn.XLOOKUP(A198,indice!A:A,indice!C:C)</f>
@@ -8481,13 +8490,13 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>481</v>
+        <v>354</v>
       </c>
       <c r="B199" t="s">
-        <v>482</v>
+        <v>58</v>
       </c>
       <c r="C199" s="57">
-        <v>169028.96</v>
+        <v>13042.91</v>
       </c>
       <c r="D199" s="57">
         <v>0</v>
@@ -8499,49 +8508,49 @@
         <v>0</v>
       </c>
       <c r="G199" s="57">
-        <v>169028.96</v>
+        <v>13042.91</v>
       </c>
       <c r="H199">
         <f>_xlfn.XLOOKUP(A199,indice!A:A,indice!C:C)</f>
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B200" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C200" s="57">
-        <v>-70000</v>
+        <v>-314043.59000000003</v>
       </c>
       <c r="D200" s="57">
         <v>0</v>
       </c>
       <c r="E200" s="57">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="F200" s="57">
-        <v>0</v>
+        <v>-5.13</v>
       </c>
       <c r="G200" s="57">
-        <v>-70000</v>
-      </c>
-      <c r="H200" t="str">
+        <v>-314048.71999999997</v>
+      </c>
+      <c r="H200">
         <f>_xlfn.XLOOKUP(A200,indice!A:A,indice!C:C)</f>
-        <v>S</v>
+        <v>12</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>371</v>
+        <v>448</v>
       </c>
       <c r="B201" t="s">
-        <v>372</v>
+        <v>449</v>
       </c>
       <c r="C201" s="57">
-        <v>-70000</v>
+        <v>43241.47</v>
       </c>
       <c r="D201" s="57">
         <v>0</v>
@@ -8553,7 +8562,7 @@
         <v>0</v>
       </c>
       <c r="G201" s="57">
-        <v>-70000</v>
+        <v>43241.47</v>
       </c>
       <c r="H201">
         <f>_xlfn.XLOOKUP(A201,indice!A:A,indice!C:C)</f>
@@ -8561,11 +8570,200 @@
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D202" s="60">
-        <v>101005343.83</v>
-      </c>
-      <c r="E202" s="60">
-        <v>101005343.83</v>
+      <c r="A202" t="s">
+        <v>357</v>
+      </c>
+      <c r="B202" t="s">
+        <v>358</v>
+      </c>
+      <c r="C202" s="57">
+        <v>-4245020.5199999996</v>
+      </c>
+      <c r="D202" s="57">
+        <v>0</v>
+      </c>
+      <c r="E202" s="57">
+        <v>4661.4799999999996</v>
+      </c>
+      <c r="F202" s="57">
+        <v>-4661.4799999999996</v>
+      </c>
+      <c r="G202" s="57">
+        <v>-4249682</v>
+      </c>
+      <c r="H202">
+        <f>_xlfn.XLOOKUP(A202,indice!A:A,indice!C:C)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>359</v>
+      </c>
+      <c r="B203" t="s">
+        <v>360</v>
+      </c>
+      <c r="C203" s="57">
+        <v>33009.449999999997</v>
+      </c>
+      <c r="D203" s="57">
+        <v>24875.360000000001</v>
+      </c>
+      <c r="E203" s="57">
+        <v>0</v>
+      </c>
+      <c r="F203" s="57">
+        <v>24875.360000000001</v>
+      </c>
+      <c r="G203" s="57">
+        <v>57884.81</v>
+      </c>
+      <c r="H203">
+        <f>_xlfn.XLOOKUP(A203,indice!A:A,indice!C:C)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>361</v>
+      </c>
+      <c r="B204" t="s">
+        <v>362</v>
+      </c>
+      <c r="C204" s="57">
+        <v>-187531.87</v>
+      </c>
+      <c r="D204" s="57">
+        <v>0</v>
+      </c>
+      <c r="E204" s="57">
+        <v>0</v>
+      </c>
+      <c r="F204" s="57">
+        <v>0</v>
+      </c>
+      <c r="G204" s="57">
+        <v>-187531.87</v>
+      </c>
+      <c r="H204">
+        <f>_xlfn.XLOOKUP(A204,indice!A:A,indice!C:C)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>363</v>
+      </c>
+      <c r="B205" t="s">
+        <v>364</v>
+      </c>
+      <c r="C205" s="57">
+        <v>78748.75</v>
+      </c>
+      <c r="D205" s="57">
+        <v>0</v>
+      </c>
+      <c r="E205" s="57">
+        <v>0</v>
+      </c>
+      <c r="F205" s="57">
+        <v>0</v>
+      </c>
+      <c r="G205" s="57">
+        <v>78748.75</v>
+      </c>
+      <c r="H205">
+        <f>_xlfn.XLOOKUP(A205,indice!A:A,indice!C:C)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>481</v>
+      </c>
+      <c r="B206" t="s">
+        <v>482</v>
+      </c>
+      <c r="C206" s="57">
+        <v>169028.96</v>
+      </c>
+      <c r="D206" s="57">
+        <v>0</v>
+      </c>
+      <c r="E206" s="57">
+        <v>0</v>
+      </c>
+      <c r="F206" s="57">
+        <v>0</v>
+      </c>
+      <c r="G206" s="57">
+        <v>169028.96</v>
+      </c>
+      <c r="H206">
+        <f>_xlfn.XLOOKUP(A206,indice!A:A,indice!C:C)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>369</v>
+      </c>
+      <c r="B207" t="s">
+        <v>370</v>
+      </c>
+      <c r="C207" s="57">
+        <v>-70000</v>
+      </c>
+      <c r="D207" s="57">
+        <v>0</v>
+      </c>
+      <c r="E207" s="57">
+        <v>0</v>
+      </c>
+      <c r="F207" s="57">
+        <v>0</v>
+      </c>
+      <c r="G207" s="57">
+        <v>-70000</v>
+      </c>
+      <c r="H207" t="str">
+        <f>_xlfn.XLOOKUP(A207,indice!A:A,indice!C:C)</f>
+        <v>S</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>371</v>
+      </c>
+      <c r="B208" t="s">
+        <v>372</v>
+      </c>
+      <c r="C208" s="57">
+        <v>-70000</v>
+      </c>
+      <c r="D208" s="57">
+        <v>0</v>
+      </c>
+      <c r="E208" s="57">
+        <v>0</v>
+      </c>
+      <c r="F208" s="57">
+        <v>0</v>
+      </c>
+      <c r="G208" s="57">
+        <v>-70000</v>
+      </c>
+      <c r="H208">
+        <f>_xlfn.XLOOKUP(A208,indice!A:A,indice!C:C)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D209" s="60">
+        <v>51401674.18</v>
+      </c>
+      <c r="E209" s="60">
+        <v>51401674.18</v>
       </c>
     </row>
   </sheetData>
@@ -8576,7 +8774,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{008E94EF-66E6-430E-869F-D768A54772BC}">
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -9340,11 +9538,11 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>143</v>
+      <c r="A55" t="s">
+        <v>523</v>
+      </c>
+      <c r="B55" t="s">
+        <v>277</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>374</v>
@@ -9355,10 +9553,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>374</v>
@@ -9369,10 +9567,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>374</v>
@@ -9383,10 +9581,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>374</v>
@@ -9397,10 +9595,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>374</v>
@@ -9411,10 +9609,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>374</v>
@@ -9425,10 +9623,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>374</v>
@@ -9439,10 +9637,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>374</v>
@@ -9453,10 +9651,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>374</v>
@@ -9467,10 +9665,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>374</v>
@@ -9481,10 +9679,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>374</v>
@@ -9495,10 +9693,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>374</v>
@@ -9509,10 +9707,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>374</v>
@@ -9523,10 +9721,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>374</v>
@@ -9537,10 +9735,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>374</v>
@@ -9550,11 +9748,11 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>394</v>
+      <c r="A70" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>374</v>
@@ -9564,11 +9762,11 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>173</v>
+      <c r="A71" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>394</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>374</v>
@@ -9579,10 +9777,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>374</v>
@@ -9592,11 +9790,11 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>238</v>
+      <c r="A73" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>374</v>
@@ -9606,11 +9804,11 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>177</v>
+      <c r="A74" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>374</v>
@@ -9621,10 +9819,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>374</v>
@@ -9635,10 +9833,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>374</v>
@@ -9649,10 +9847,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>374</v>
@@ -9662,11 +9860,11 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>427</v>
-      </c>
-      <c r="B78" t="s">
-        <v>428</v>
+      <c r="A78" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>374</v>
@@ -9676,11 +9874,11 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>185</v>
+      <c r="A79" t="s">
+        <v>427</v>
+      </c>
+      <c r="B79" t="s">
+        <v>428</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>374</v>
@@ -9691,10 +9889,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>374</v>
@@ -9705,10 +9903,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>374</v>
@@ -9718,11 +9916,11 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="42" t="s">
-        <v>441</v>
-      </c>
-      <c r="B82" s="41" t="s">
-        <v>442</v>
+      <c r="A82" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>374</v>
@@ -9732,11 +9930,11 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>191</v>
+      <c r="A83" s="42" t="s">
+        <v>441</v>
+      </c>
+      <c r="B83" s="41" t="s">
+        <v>442</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>374</v>
@@ -9747,10 +9945,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>374</v>
@@ -9760,11 +9958,11 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="42" t="s">
-        <v>443</v>
-      </c>
-      <c r="B85" s="41" t="s">
-        <v>444</v>
+      <c r="A85" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>374</v>
@@ -9774,11 +9972,11 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>195</v>
+      <c r="A86" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="B86" s="41" t="s">
+        <v>444</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>374</v>
@@ -9788,11 +9986,11 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>516</v>
-      </c>
-      <c r="B87" t="s">
-        <v>315</v>
+      <c r="A87" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>374</v>
@@ -9802,11 +10000,11 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>197</v>
+      <c r="A88" t="s">
+        <v>516</v>
+      </c>
+      <c r="B88" t="s">
+        <v>315</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>374</v>
@@ -9817,10 +10015,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>374</v>
@@ -9831,10 +10029,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>374</v>
@@ -9845,10 +10043,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>374</v>
@@ -9859,10 +10057,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>374</v>
@@ -9873,10 +10071,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>374</v>
@@ -9887,10 +10085,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>374</v>
@@ -9901,10 +10099,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>374</v>
@@ -9915,10 +10113,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>374</v>
@@ -9929,10 +10127,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>374</v>
@@ -9943,10 +10141,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>374</v>
@@ -9957,10 +10155,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>374</v>
@@ -9971,38 +10169,38 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C101">
-        <v>10</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>15</v>
+        <v>221</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C102">
         <v>10</v>
@@ -10013,10 +10211,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C103">
         <v>10</v>
@@ -10027,10 +10225,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="C104">
         <v>10</v>
@@ -10041,10 +10239,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C105">
         <v>10</v>
@@ -10055,10 +10253,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
       <c r="C106">
         <v>10</v>
@@ -10068,11 +10266,11 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>145</v>
+      <c r="A107" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -10082,11 +10280,11 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="35" t="s">
-        <v>412</v>
-      </c>
-      <c r="B108" s="34" t="s">
-        <v>413</v>
+      <c r="A108" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="C108">
         <v>10</v>
@@ -10096,11 +10294,11 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>151</v>
+      <c r="A109" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="B109" s="34" t="s">
+        <v>413</v>
       </c>
       <c r="C109">
         <v>10</v>
@@ -10111,10 +10309,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C110">
         <v>10</v>
@@ -10125,10 +10323,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>232</v>
+        <v>155</v>
       </c>
       <c r="C111">
         <v>10</v>
@@ -10139,10 +10337,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="C112">
         <v>10</v>
@@ -10152,11 +10350,11 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="50" t="s">
-        <v>473</v>
-      </c>
-      <c r="B113" s="50" t="s">
-        <v>165</v>
+      <c r="A113" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="C113">
         <v>10</v>
@@ -10166,11 +10364,11 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="35" t="s">
-        <v>414</v>
-      </c>
-      <c r="B114" s="34" t="s">
-        <v>171</v>
+      <c r="A114" s="50" t="s">
+        <v>473</v>
+      </c>
+      <c r="B114" s="50" t="s">
+        <v>165</v>
       </c>
       <c r="C114">
         <v>10</v>
@@ -10180,11 +10378,11 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>173</v>
+      <c r="A115" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="B115" s="34" t="s">
+        <v>171</v>
       </c>
       <c r="C115">
         <v>10</v>
@@ -10195,10 +10393,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="C116">
         <v>10</v>
@@ -10209,10 +10407,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C117">
         <v>10</v>
@@ -10222,11 +10420,11 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="42" t="s">
-        <v>445</v>
-      </c>
-      <c r="B118" s="41" t="s">
-        <v>177</v>
+      <c r="A118" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="C118">
         <v>10</v>
@@ -10236,11 +10434,11 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>179</v>
+      <c r="A119" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="B119" s="41" t="s">
+        <v>177</v>
       </c>
       <c r="C119">
         <v>10</v>
@@ -10251,10 +10449,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C120">
         <v>10</v>
@@ -10264,11 +10462,11 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>468</v>
-      </c>
-      <c r="B121" t="s">
-        <v>189</v>
+      <c r="A121" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="C121">
         <v>10</v>
@@ -10278,11 +10476,11 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>191</v>
+      <c r="A122" t="s">
+        <v>468</v>
+      </c>
+      <c r="B122" t="s">
+        <v>189</v>
       </c>
       <c r="C122">
         <v>10</v>
@@ -10293,10 +10491,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="C123">
         <v>10</v>
@@ -10306,11 +10504,11 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="49" t="s">
-        <v>460</v>
-      </c>
-      <c r="B124" s="48" t="s">
-        <v>461</v>
+      <c r="A124" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="C124">
         <v>10</v>
@@ -10320,11 +10518,11 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>201</v>
+      <c r="A125" s="49" t="s">
+        <v>460</v>
+      </c>
+      <c r="B125" s="48" t="s">
+        <v>461</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -10335,10 +10533,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C126">
         <v>10</v>
@@ -10349,10 +10547,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="C127">
         <v>10</v>
@@ -10363,10 +10561,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="C128">
         <v>10</v>
@@ -10377,10 +10575,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C129">
         <v>10</v>
@@ -10391,10 +10589,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C130">
         <v>10</v>
@@ -10405,10 +10603,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
       <c r="C131">
         <v>10</v>
@@ -10419,10 +10617,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="C132">
         <v>10</v>
@@ -10433,10 +10631,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>255</v>
+        <v>217</v>
       </c>
       <c r="C133">
         <v>10</v>
@@ -10447,10 +10645,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C134">
         <v>10</v>
@@ -10461,10 +10659,10 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C135">
         <v>10</v>
@@ -10474,11 +10672,11 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>498</v>
-      </c>
-      <c r="B136" t="s">
-        <v>499</v>
+      <c r="A136" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="C136">
         <v>10</v>
@@ -10488,11 +10686,11 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="42" t="s">
-        <v>446</v>
-      </c>
-      <c r="B137" s="41" t="s">
-        <v>447</v>
+      <c r="A137" t="s">
+        <v>498</v>
+      </c>
+      <c r="B137" t="s">
+        <v>499</v>
       </c>
       <c r="C137">
         <v>10</v>
@@ -10502,39 +10700,39 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>375</v>
+      <c r="A138" s="42" t="s">
+        <v>446</v>
+      </c>
+      <c r="B138" s="41" t="s">
+        <v>447</v>
+      </c>
+      <c r="C138">
+        <v>10</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C139">
-        <v>11</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>16</v>
+        <v>261</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C140">
         <v>11</v>
@@ -10545,10 +10743,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C141">
         <v>11</v>
@@ -10559,10 +10757,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="C142">
         <v>11</v>
@@ -10573,10 +10771,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>63</v>
+        <v>266</v>
       </c>
       <c r="C143">
         <v>11</v>
@@ -10587,10 +10785,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C144">
         <v>11</v>
@@ -10601,10 +10799,10 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>270</v>
+        <v>64</v>
       </c>
       <c r="C145">
         <v>11</v>
@@ -10615,10 +10813,10 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="C146">
         <v>11</v>
@@ -10629,10 +10827,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>273</v>
+        <v>141</v>
       </c>
       <c r="C147">
         <v>11</v>
@@ -10643,10 +10841,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C148">
         <v>11</v>
@@ -10657,10 +10855,10 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C149">
         <v>11</v>
@@ -10670,11 +10868,11 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>143</v>
+      <c r="A150" t="s">
+        <v>524</v>
+      </c>
+      <c r="B150" t="s">
+        <v>525</v>
       </c>
       <c r="C150">
         <v>11</v>
@@ -10685,10 +10883,10 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>145</v>
+        <v>277</v>
       </c>
       <c r="C151">
         <v>11</v>
@@ -10699,10 +10897,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C152">
         <v>11</v>
@@ -10713,10 +10911,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>282</v>
+        <v>145</v>
       </c>
       <c r="C153">
         <v>11</v>
@@ -10727,10 +10925,10 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C154">
         <v>11</v>
@@ -10741,10 +10939,10 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>153</v>
+        <v>282</v>
       </c>
       <c r="C155">
         <v>11</v>
@@ -10755,10 +10953,10 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C156">
         <v>11</v>
@@ -10769,10 +10967,10 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C157">
         <v>11</v>
@@ -10783,10 +10981,10 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>288</v>
+        <v>155</v>
       </c>
       <c r="C158">
         <v>11</v>
@@ -10797,10 +10995,10 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C159">
         <v>11</v>
@@ -10811,10 +11009,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>163</v>
+        <v>288</v>
       </c>
       <c r="C160">
         <v>11</v>
@@ -10825,10 +11023,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C161">
         <v>11</v>
@@ -10839,10 +11037,10 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C162">
         <v>11</v>
@@ -10853,10 +11051,10 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C163">
         <v>11</v>
@@ -10867,10 +11065,10 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="C164">
         <v>11</v>
@@ -10881,10 +11079,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>297</v>
+        <v>169</v>
       </c>
       <c r="C165">
         <v>11</v>
@@ -10895,10 +11093,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>171</v>
+        <v>295</v>
       </c>
       <c r="C166">
         <v>11</v>
@@ -10909,10 +11107,10 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C167">
         <v>11</v>
@@ -10922,11 +11120,11 @@
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="B168" s="9" t="s">
-        <v>394</v>
+      <c r="A168" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="C168">
         <v>11</v>
@@ -10937,10 +11135,10 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C169">
         <v>11</v>
@@ -10950,11 +11148,11 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>173</v>
+      <c r="A170" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>394</v>
       </c>
       <c r="C170">
         <v>11</v>
@@ -10965,10 +11163,10 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>175</v>
+        <v>302</v>
       </c>
       <c r="C171">
         <v>11</v>
@@ -10979,10 +11177,10 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>306</v>
+        <v>173</v>
       </c>
       <c r="C172">
         <v>11</v>
@@ -10993,10 +11191,10 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="C173">
         <v>11</v>
@@ -11006,11 +11204,11 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="50" t="s">
-        <v>474</v>
-      </c>
-      <c r="B174" s="50" t="s">
-        <v>177</v>
+      <c r="A174" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>306</v>
       </c>
       <c r="C174">
         <v>11</v>
@@ -11021,10 +11219,10 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="C175">
         <v>11</v>
@@ -11034,11 +11232,11 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>189</v>
+      <c r="A176" s="50" t="s">
+        <v>474</v>
+      </c>
+      <c r="B176" s="50" t="s">
+        <v>177</v>
       </c>
       <c r="C176">
         <v>11</v>
@@ -11049,10 +11247,10 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C177">
         <v>11</v>
@@ -11063,10 +11261,10 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="C178">
         <v>11</v>
@@ -11076,11 +11274,11 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="44" t="s">
-        <v>451</v>
-      </c>
-      <c r="B179" s="43" t="s">
-        <v>444</v>
+      <c r="A179" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="C179">
         <v>11</v>
@@ -11091,10 +11289,10 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>195</v>
+        <v>312</v>
       </c>
       <c r="C180">
         <v>11</v>
@@ -11104,11 +11302,11 @@
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>315</v>
+      <c r="A181" s="44" t="s">
+        <v>451</v>
+      </c>
+      <c r="B181" s="43" t="s">
+        <v>444</v>
       </c>
       <c r="C181">
         <v>11</v>
@@ -11119,10 +11317,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C182">
         <v>11</v>
@@ -11133,10 +11331,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>201</v>
+        <v>315</v>
       </c>
       <c r="C183">
         <v>11</v>
@@ -11147,10 +11345,10 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C184">
         <v>11</v>
@@ -11161,10 +11359,10 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C185">
         <v>11</v>
@@ -11175,10 +11373,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C186">
         <v>11</v>
@@ -11189,10 +11387,10 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C187">
         <v>11</v>
@@ -11203,10 +11401,10 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C188">
         <v>11</v>
@@ -11217,10 +11415,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C189">
         <v>11</v>
@@ -11231,10 +11429,10 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>325</v>
+        <v>211</v>
       </c>
       <c r="C190">
         <v>11</v>
@@ -11245,10 +11443,10 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>327</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>11</v>
@@ -11258,11 +11456,11 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="B192" s="9" t="s">
-        <v>399</v>
+      <c r="A192" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>325</v>
       </c>
       <c r="C192">
         <v>11</v>
@@ -11273,10 +11471,10 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C193">
         <v>11</v>
@@ -11286,11 +11484,11 @@
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>217</v>
+      <c r="A194" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>399</v>
       </c>
       <c r="C194">
         <v>11</v>
@@ -11300,11 +11498,11 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="50" t="s">
-        <v>475</v>
-      </c>
-      <c r="B195" s="50" t="s">
-        <v>476</v>
+      <c r="A195" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="C195">
         <v>11</v>
@@ -11314,11 +11512,11 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>486</v>
-      </c>
-      <c r="B196" t="s">
-        <v>487</v>
+      <c r="A196" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="C196">
         <v>11</v>
@@ -11328,11 +11526,11 @@
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="39" t="s">
-        <v>423</v>
-      </c>
-      <c r="B197" s="38" t="s">
-        <v>424</v>
+      <c r="A197" s="50" t="s">
+        <v>475</v>
+      </c>
+      <c r="B197" s="50" t="s">
+        <v>476</v>
       </c>
       <c r="C197">
         <v>11</v>
@@ -11342,11 +11540,11 @@
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>332</v>
+      <c r="A198" t="s">
+        <v>486</v>
+      </c>
+      <c r="B198" t="s">
+        <v>487</v>
       </c>
       <c r="C198">
         <v>11</v>
@@ -11356,11 +11554,11 @@
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>429</v>
-      </c>
-      <c r="B199" t="s">
-        <v>430</v>
+      <c r="A199" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="B199" s="38" t="s">
+        <v>424</v>
       </c>
       <c r="C199">
         <v>11</v>
@@ -11371,10 +11569,10 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C200">
         <v>11</v>
@@ -11385,10 +11583,10 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>488</v>
+        <v>429</v>
       </c>
       <c r="B201" t="s">
-        <v>489</v>
+        <v>430</v>
       </c>
       <c r="C201">
         <v>11</v>
@@ -11398,11 +11596,11 @@
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" s="49" t="s">
-        <v>462</v>
-      </c>
-      <c r="B202" s="48" t="s">
-        <v>463</v>
+      <c r="A202" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="C202">
         <v>11</v>
@@ -11412,11 +11610,11 @@
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A203" s="49" t="s">
-        <v>464</v>
-      </c>
-      <c r="B203" s="48" t="s">
-        <v>465</v>
+      <c r="A203" t="s">
+        <v>488</v>
+      </c>
+      <c r="B203" t="s">
+        <v>489</v>
       </c>
       <c r="C203">
         <v>11</v>
@@ -11426,53 +11624,53 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>373</v>
+      <c r="A204" s="49" t="s">
+        <v>462</v>
+      </c>
+      <c r="B204" s="48" t="s">
+        <v>463</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>375</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>500</v>
-      </c>
-      <c r="B205" t="s">
-        <v>501</v>
+      <c r="A205" s="49" t="s">
+        <v>464</v>
+      </c>
+      <c r="B205" s="48" t="s">
+        <v>465</v>
       </c>
       <c r="C205">
-        <v>14</v>
-      </c>
-      <c r="D205" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C206">
-        <v>14</v>
-      </c>
-      <c r="D206" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="C206" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>339</v>
+      <c r="A207" t="s">
+        <v>500</v>
+      </c>
+      <c r="B207" t="s">
+        <v>501</v>
       </c>
       <c r="C207">
         <v>14</v>
@@ -11483,10 +11681,10 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C208">
         <v>14</v>
@@ -11497,10 +11695,10 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C209">
         <v>14</v>
@@ -11511,10 +11709,10 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C210">
         <v>14</v>
@@ -11525,10 +11723,10 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C211">
         <v>14</v>
@@ -11539,10 +11737,10 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C212">
         <v>14</v>
@@ -11552,11 +11750,11 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>469</v>
-      </c>
-      <c r="B213" t="s">
-        <v>470</v>
+      <c r="A213" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>347</v>
       </c>
       <c r="C213">
         <v>14</v>
@@ -11566,11 +11764,11 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="44" t="s">
-        <v>452</v>
-      </c>
-      <c r="B214" s="43" t="s">
-        <v>453</v>
+      <c r="A214" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>349</v>
       </c>
       <c r="C214">
         <v>14</v>
@@ -11580,11 +11778,11 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="50" t="s">
-        <v>477</v>
-      </c>
-      <c r="B215" s="50" t="s">
-        <v>478</v>
+      <c r="A215" t="s">
+        <v>469</v>
+      </c>
+      <c r="B215" t="s">
+        <v>470</v>
       </c>
       <c r="C215">
         <v>14</v>
@@ -11594,11 +11792,11 @@
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>484</v>
-      </c>
-      <c r="B216" t="s">
-        <v>485</v>
+      <c r="A216" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="B216" s="43" t="s">
+        <v>453</v>
       </c>
       <c r="C216">
         <v>14</v>
@@ -11608,14 +11806,14 @@
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>490</v>
-      </c>
-      <c r="B217" t="s">
-        <v>491</v>
+      <c r="A217" s="50" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="50" t="s">
+        <v>478</v>
       </c>
       <c r="C217">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>18</v>
@@ -11623,13 +11821,13 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="B218" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C218">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>18</v>
@@ -11637,13 +11835,13 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="B219" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="C219">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>18</v>
@@ -11651,13 +11849,13 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="B220" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="C220">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>18</v>
@@ -11665,10 +11863,10 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="B221" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C221">
         <v>14</v>
@@ -11678,53 +11876,53 @@
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>373</v>
+      <c r="A222" t="s">
+        <v>511</v>
+      </c>
+      <c r="B222" t="s">
+        <v>512</v>
+      </c>
+      <c r="C222">
+        <v>14</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>375</v>
+        <v>18</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>56</v>
+      <c r="A223" t="s">
+        <v>517</v>
+      </c>
+      <c r="B223" t="s">
+        <v>518</v>
       </c>
       <c r="C223">
-        <v>12</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>52</v>
+        <v>14</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C224">
-        <v>12</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C225">
         <v>12</v>
@@ -11733,12 +11931,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>356</v>
+        <v>57</v>
       </c>
       <c r="C226">
         <v>12</v>
@@ -11747,12 +11945,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A227" s="44" t="s">
-        <v>454</v>
-      </c>
-      <c r="B227" s="43" t="s">
-        <v>455</v>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C227">
         <v>12</v>
@@ -11761,12 +11959,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>496</v>
-      </c>
-      <c r="B228" t="s">
-        <v>497</v>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>356</v>
       </c>
       <c r="C228">
         <v>12</v>
@@ -11775,12 +11973,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>506</v>
-      </c>
-      <c r="B229" t="s">
-        <v>55</v>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="44" t="s">
+        <v>454</v>
+      </c>
+      <c r="B229" s="43" t="s">
+        <v>455</v>
       </c>
       <c r="C229">
         <v>12</v>
@@ -11789,12 +11987,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A230" s="42" t="s">
-        <v>448</v>
-      </c>
-      <c r="B230" s="41" t="s">
-        <v>449</v>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>496</v>
+      </c>
+      <c r="B230" t="s">
+        <v>497</v>
       </c>
       <c r="C230">
         <v>12</v>
@@ -11803,12 +12001,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B231" t="s">
-        <v>508</v>
+        <v>55</v>
       </c>
       <c r="C231">
         <v>12</v>
@@ -11817,12 +12015,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A232" s="49" t="s">
-        <v>466</v>
-      </c>
-      <c r="B232" s="48" t="s">
-        <v>467</v>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="42" t="s">
+        <v>448</v>
+      </c>
+      <c r="B232" s="41" t="s">
+        <v>449</v>
       </c>
       <c r="C232">
         <v>12</v>
@@ -11831,68 +12029,68 @@
         <v>52</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A233" s="6" t="s">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>507</v>
+      </c>
+      <c r="B233" t="s">
+        <v>508</v>
+      </c>
+      <c r="C233">
+        <v>12</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="49" t="s">
+        <v>466</v>
+      </c>
+      <c r="B234" s="48" t="s">
+        <v>467</v>
+      </c>
+      <c r="C234">
+        <v>12</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="B233" s="5" t="s">
+      <c r="B235" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="C233">
+      <c r="C235">
         <v>3</v>
       </c>
-      <c r="D233" s="4" t="s">
+      <c r="D235" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A234" s="37" t="s">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" s="37" t="s">
         <v>419</v>
       </c>
-      <c r="B234" s="36" t="s">
+      <c r="B236" s="36" t="s">
         <v>420</v>
       </c>
-      <c r="C234">
+      <c r="C236">
         <v>3</v>
       </c>
-      <c r="D234" s="4" t="s">
+      <c r="D236" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A235" s="6" t="s">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="B235" s="5" t="s">
+      <c r="B237" s="5" t="s">
         <v>360</v>
-      </c>
-      <c r="C235">
-        <v>12</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A236" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="B236" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="C236">
-        <v>12</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>431</v>
-      </c>
-      <c r="B237" t="s">
-        <v>432</v>
       </c>
       <c r="C237">
         <v>12</v>
@@ -11901,12 +12099,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C238">
         <v>12</v>
@@ -11915,12 +12113,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A239" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="B239" s="5" t="s">
-        <v>366</v>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>431</v>
+      </c>
+      <c r="B239" t="s">
+        <v>432</v>
       </c>
       <c r="C239">
         <v>12</v>
@@ -11929,27 +12127,26 @@
         <v>52</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" s="45" t="s">
-        <v>367</v>
-      </c>
-      <c r="B240" s="46" t="s">
-        <v>368</v>
-      </c>
-      <c r="C240" s="40">
-        <v>21</v>
-      </c>
-      <c r="D240" s="47" t="s">
-        <v>403</v>
-      </c>
-      <c r="E240" s="40"/>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C240">
+        <v>12</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>494</v>
-      </c>
-      <c r="B241" t="s">
-        <v>495</v>
+      <c r="A241" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>366</v>
       </c>
       <c r="C241">
         <v>12</v>
@@ -11957,84 +12154,85 @@
       <c r="D241" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E241" s="40"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A242" s="44" t="s">
+      <c r="A242" s="45" t="s">
+        <v>367</v>
+      </c>
+      <c r="B242" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="C242" s="40">
+        <v>21</v>
+      </c>
+      <c r="D242" s="47" t="s">
+        <v>403</v>
+      </c>
+      <c r="E242" s="40"/>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>494</v>
+      </c>
+      <c r="B243" t="s">
+        <v>495</v>
+      </c>
+      <c r="C243">
+        <v>12</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E243" s="40"/>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" s="44" t="s">
         <v>456</v>
       </c>
-      <c r="B242" s="43" t="s">
+      <c r="B244" s="43" t="s">
         <v>457</v>
       </c>
-      <c r="C242">
+      <c r="C244">
         <v>12</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="D244" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A243" s="44" t="s">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" s="44" t="s">
         <v>458</v>
       </c>
-      <c r="B243" s="43" t="s">
+      <c r="B245" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="C243">
+      <c r="C245">
         <v>23</v>
       </c>
-      <c r="D243" t="s">
+      <c r="D245" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A244" s="10" t="s">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="B244" s="9" t="s">
+      <c r="B246" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="C244">
+      <c r="C246">
         <v>20</v>
       </c>
-      <c r="D244" s="7" t="s">
+      <c r="D246" s="7" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A245" s="35" t="s">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" s="35" t="s">
         <v>415</v>
       </c>
-      <c r="B245" s="34" t="s">
+      <c r="B247" s="34" t="s">
         <v>416</v>
-      </c>
-      <c r="C245">
-        <v>12</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A246" s="35" t="s">
-        <v>417</v>
-      </c>
-      <c r="B246" s="34" t="s">
-        <v>418</v>
-      </c>
-      <c r="C246">
-        <v>12</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A247" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="B247" s="36" t="s">
-        <v>422</v>
       </c>
       <c r="C247">
         <v>12</v>
@@ -12044,11 +12242,11 @@
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A248" s="50" t="s">
-        <v>479</v>
-      </c>
-      <c r="B248" s="50" t="s">
-        <v>480</v>
+      <c r="A248" s="35" t="s">
+        <v>417</v>
+      </c>
+      <c r="B248" s="34" t="s">
+        <v>418</v>
       </c>
       <c r="C248">
         <v>12</v>
@@ -12058,100 +12256,128 @@
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A249" s="50" t="s">
+      <c r="A249" s="37" t="s">
+        <v>421</v>
+      </c>
+      <c r="B249" s="36" t="s">
+        <v>422</v>
+      </c>
+      <c r="C249">
+        <v>12</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" s="50" t="s">
+        <v>479</v>
+      </c>
+      <c r="B250" s="50" t="s">
+        <v>480</v>
+      </c>
+      <c r="C250">
+        <v>12</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" s="50" t="s">
         <v>481</v>
       </c>
-      <c r="B249" s="50" t="s">
+      <c r="B251" s="50" t="s">
         <v>482</v>
       </c>
-      <c r="C249">
+      <c r="C251">
         <v>20</v>
       </c>
-      <c r="D249" s="7" t="s">
+      <c r="D251" s="7" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
         <v>519</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B252" t="s">
         <v>520</v>
       </c>
-      <c r="C250">
+      <c r="C252">
         <v>20</v>
       </c>
-      <c r="D250" s="7" t="s">
+      <c r="D252" s="7" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A251" s="6" t="s">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="B251" s="5" t="s">
+      <c r="B253" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="C251" s="3" t="s">
+      <c r="C253" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D251" s="1" t="s">
+      <c r="D253" s="1" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A252" s="6" t="s">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="B252" s="5" t="s">
+      <c r="B254" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C252">
+      <c r="C254">
         <v>12</v>
       </c>
-      <c r="D252" s="1" t="s">
+      <c r="D254" s="1" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>471</v>
-      </c>
-      <c r="B253" t="s">
-        <v>472</v>
-      </c>
-      <c r="C253">
-        <v>12</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>502</v>
-      </c>
-      <c r="B254" t="s">
-        <v>503</v>
-      </c>
-      <c r="C254">
-        <v>20</v>
-      </c>
-      <c r="D254" s="7" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>471</v>
+      </c>
+      <c r="B255" t="s">
+        <v>472</v>
+      </c>
+      <c r="C255">
+        <v>12</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>502</v>
+      </c>
+      <c r="B256" t="s">
+        <v>503</v>
+      </c>
+      <c r="C256">
+        <v>20</v>
+      </c>
+      <c r="D256" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
         <v>504</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B257" t="s">
         <v>505</v>
       </c>
-      <c r="C255">
+      <c r="C257">
         <v>20</v>
       </c>
-      <c r="D255" s="7" t="s">
+      <c r="D257" s="7" t="s">
         <v>402</v>
       </c>
     </row>
